--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1124"/>
+  <dimension ref="A1:U1224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -73463,9 +73463,6509 @@
         <v/>
       </c>
     </row>
+    <row r="1125">
+      <c r="A1125" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1125" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>Ljubljana Airport</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>airport</v>
+      </c>
+      <c r="E1125">
+        <v>1</v>
+      </c>
+      <c r="F1125" t="str">
+        <v>✈️</v>
+      </c>
+      <c r="G1125" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1125" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1125" t="str">
+        <v/>
+      </c>
+      <c r="J1125" t="str">
+        <v>46.228624</v>
+      </c>
+      <c r="K1125" t="str">
+        <v>14.454207</v>
+      </c>
+      <c r="L1125" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1125" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1125" t="str">
+        <v/>
+      </c>
+      <c r="O1125" t="str">
+        <v/>
+      </c>
+      <c r="P1125" t="str">
+        <v/>
+      </c>
+      <c r="Q1125" t="str">
+        <v/>
+      </c>
+      <c r="R1125" t="str">
+        <v/>
+      </c>
+      <c r="S1125" t="str">
+        <v/>
+      </c>
+      <c r="T1125" t="str">
+        <v/>
+      </c>
+      <c r="U1125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1126" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1126" t="str">
+        <v>Ljubljana Train Station Ticket Office</v>
+      </c>
+      <c r="D1126" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1126">
+        <v>1</v>
+      </c>
+      <c r="F1126" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1126" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1126" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1126" t="str">
+        <v/>
+      </c>
+      <c r="J1126" t="str">
+        <v>46.058024</v>
+      </c>
+      <c r="K1126" t="str">
+        <v>14.510022</v>
+      </c>
+      <c r="L1126" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1126" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1126" t="str">
+        <v/>
+      </c>
+      <c r="O1126" t="str">
+        <v/>
+      </c>
+      <c r="P1126" t="str">
+        <v/>
+      </c>
+      <c r="Q1126" t="str">
+        <v/>
+      </c>
+      <c r="R1126" t="str">
+        <v/>
+      </c>
+      <c r="S1126" t="str">
+        <v/>
+      </c>
+      <c r="T1126" t="str">
+        <v/>
+      </c>
+      <c r="U1126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1127" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1127" t="str">
+        <v>Exe Lev</v>
+      </c>
+      <c r="D1127" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1127">
+        <v>1</v>
+      </c>
+      <c r="F1127" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1127" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1127" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1127" t="str">
+        <v/>
+      </c>
+      <c r="J1127" t="str">
+        <v>46.05625</v>
+      </c>
+      <c r="K1127" t="str">
+        <v>14.502545</v>
+      </c>
+      <c r="L1127" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1127" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1127" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1127" t="str">
+        <v/>
+      </c>
+      <c r="P1127" t="str">
+        <v/>
+      </c>
+      <c r="Q1127" t="str">
+        <v/>
+      </c>
+      <c r="R1127" t="str">
+        <v/>
+      </c>
+      <c r="S1127" t="str">
+        <v>https://www.hotels.com/ho134298/hotel-lev-ljubljana-slovenia/</v>
+      </c>
+      <c r="T1127" t="str">
+        <v/>
+      </c>
+      <c r="U1127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1128" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1128" t="str">
+        <v>Prešernov trg</v>
+      </c>
+      <c r="D1128" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1128">
+        <v>1</v>
+      </c>
+      <c r="F1128" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1128" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1128" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1128" t="str">
+        <v/>
+      </c>
+      <c r="J1128" t="str">
+        <v>46.051471</v>
+      </c>
+      <c r="K1128" t="str">
+        <v>14.506073</v>
+      </c>
+      <c r="L1128" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1128" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1128" t="str">
+        <v/>
+      </c>
+      <c r="O1128" t="str">
+        <v/>
+      </c>
+      <c r="P1128" t="str">
+        <v/>
+      </c>
+      <c r="Q1128" t="str">
+        <v/>
+      </c>
+      <c r="R1128" t="str">
+        <v/>
+      </c>
+      <c r="S1128" t="str">
+        <v/>
+      </c>
+      <c r="T1128" t="str">
+        <v/>
+      </c>
+      <c r="U1128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1129" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1129" t="str">
+        <v>Stari trg</v>
+      </c>
+      <c r="D1129" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1129">
+        <v>1</v>
+      </c>
+      <c r="F1129" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1129" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1129" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1129" t="str">
+        <v/>
+      </c>
+      <c r="J1129" t="str">
+        <v>46.047637</v>
+      </c>
+      <c r="K1129" t="str">
+        <v>14.506302</v>
+      </c>
+      <c r="L1129" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1129" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1129" t="str">
+        <v/>
+      </c>
+      <c r="O1129" t="str">
+        <v>Llubljana Old Town</v>
+      </c>
+      <c r="P1129" t="str">
+        <v/>
+      </c>
+      <c r="Q1129" t="str">
+        <v/>
+      </c>
+      <c r="R1129" t="str">
+        <v/>
+      </c>
+      <c r="S1129" t="str">
+        <v/>
+      </c>
+      <c r="T1129" t="str">
+        <v/>
+      </c>
+      <c r="U1129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1130" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1130" t="str">
+        <v>Ljubljana Castle</v>
+      </c>
+      <c r="D1130" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1130">
+        <v>0</v>
+      </c>
+      <c r="F1130" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1130" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1130" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1130" t="str">
+        <v/>
+      </c>
+      <c r="J1130" t="str">
+        <v>46.048885</v>
+      </c>
+      <c r="K1130" t="str">
+        <v>14.508374</v>
+      </c>
+      <c r="L1130" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1130" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1130" t="str">
+        <v/>
+      </c>
+      <c r="O1130" t="str">
+        <v>Didn't get to go to the castle.</v>
+      </c>
+      <c r="P1130" t="str">
+        <v/>
+      </c>
+      <c r="Q1130" t="str">
+        <v/>
+      </c>
+      <c r="R1130" t="str">
+        <v/>
+      </c>
+      <c r="S1130" t="str">
+        <v/>
+      </c>
+      <c r="T1130" t="str">
+        <v/>
+      </c>
+      <c r="U1130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1131" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1131" t="str">
+        <v>Dragon Bridge</v>
+      </c>
+      <c r="D1131" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1131">
+        <v>1</v>
+      </c>
+      <c r="F1131" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1131" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1131" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1131" t="str">
+        <v/>
+      </c>
+      <c r="J1131" t="str">
+        <v>46.052009</v>
+      </c>
+      <c r="K1131" t="str">
+        <v>14.51031</v>
+      </c>
+      <c r="L1131" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1131" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1131" t="str">
+        <v/>
+      </c>
+      <c r="O1131" t="str">
+        <v/>
+      </c>
+      <c r="P1131" t="str">
+        <v/>
+      </c>
+      <c r="Q1131" t="str">
+        <v/>
+      </c>
+      <c r="R1131" t="str">
+        <v/>
+      </c>
+      <c r="S1131" t="str">
+        <v/>
+      </c>
+      <c r="T1131" t="str">
+        <v/>
+      </c>
+      <c r="U1131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1132" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1132" t="str">
+        <v>The Butchers' Bridge</v>
+      </c>
+      <c r="D1132" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1132">
+        <v>1</v>
+      </c>
+      <c r="F1132" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1132" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1132" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1132" t="str">
+        <v/>
+      </c>
+      <c r="J1132" t="str">
+        <v>46.051714</v>
+      </c>
+      <c r="K1132" t="str">
+        <v>14.508754</v>
+      </c>
+      <c r="L1132" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1132" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1132" t="str">
+        <v/>
+      </c>
+      <c r="O1132" t="str">
+        <v/>
+      </c>
+      <c r="P1132" t="str">
+        <v/>
+      </c>
+      <c r="Q1132" t="str">
+        <v/>
+      </c>
+      <c r="R1132" t="str">
+        <v/>
+      </c>
+      <c r="S1132" t="str">
+        <v/>
+      </c>
+      <c r="T1132" t="str">
+        <v/>
+      </c>
+      <c r="U1132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1133" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1133" t="str">
+        <v>Triple Bridge</v>
+      </c>
+      <c r="D1133" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1133">
+        <v>1</v>
+      </c>
+      <c r="F1133" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1133" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1133" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1133" t="str">
+        <v/>
+      </c>
+      <c r="J1133" t="str">
+        <v>46.051134</v>
+      </c>
+      <c r="K1133" t="str">
+        <v>14.506229</v>
+      </c>
+      <c r="L1133" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1133" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1133" t="str">
+        <v/>
+      </c>
+      <c r="O1133" t="str">
+        <v/>
+      </c>
+      <c r="P1133" t="str">
+        <v/>
+      </c>
+      <c r="Q1133" t="str">
+        <v/>
+      </c>
+      <c r="R1133" t="str">
+        <v/>
+      </c>
+      <c r="S1133" t="str">
+        <v/>
+      </c>
+      <c r="T1133" t="str">
+        <v/>
+      </c>
+      <c r="U1133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1134" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1134" t="str">
+        <v>Tivoli Park</v>
+      </c>
+      <c r="D1134" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1134" t="str">
+        <v/>
+      </c>
+      <c r="F1134" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1134" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1134" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1134" t="str">
+        <v/>
+      </c>
+      <c r="J1134" t="str">
+        <v>46.053898</v>
+      </c>
+      <c r="K1134" t="str">
+        <v>14.494913</v>
+      </c>
+      <c r="L1134" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1134" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1134" t="str">
+        <v/>
+      </c>
+      <c r="O1134" t="str">
+        <v/>
+      </c>
+      <c r="P1134" t="str">
+        <v/>
+      </c>
+      <c r="Q1134" t="str">
+        <v/>
+      </c>
+      <c r="R1134" t="str">
+        <v/>
+      </c>
+      <c r="S1134" t="str">
+        <v/>
+      </c>
+      <c r="T1134" t="str">
+        <v/>
+      </c>
+      <c r="U1134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1135" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1135" t="str">
+        <v>AKC Metelkova mesto</v>
+      </c>
+      <c r="D1135" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1135">
+        <v>0</v>
+      </c>
+      <c r="F1135" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1135" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1135" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1135" t="str">
+        <v/>
+      </c>
+      <c r="J1135" t="str">
+        <v>46.056378</v>
+      </c>
+      <c r="K1135" t="str">
+        <v>14.516823</v>
+      </c>
+      <c r="L1135" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1135" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1135" t="str">
+        <v/>
+      </c>
+      <c r="O1135" t="str">
+        <v>Didn't make it here.</v>
+      </c>
+      <c r="P1135" t="str">
+        <v/>
+      </c>
+      <c r="Q1135" t="str">
+        <v/>
+      </c>
+      <c r="R1135" t="str">
+        <v/>
+      </c>
+      <c r="S1135" t="str">
+        <v/>
+      </c>
+      <c r="T1135" t="str">
+        <v/>
+      </c>
+      <c r="U1135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1136" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1136" t="str">
+        <v>Open kitchen</v>
+      </c>
+      <c r="D1136" t="str">
+        <v>market</v>
+      </c>
+      <c r="E1136" t="str">
+        <v/>
+      </c>
+      <c r="F1136" t="str">
+        <v>🛒</v>
+      </c>
+      <c r="G1136" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1136" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1136" t="str">
+        <v/>
+      </c>
+      <c r="J1136" t="str">
+        <v>46.050999</v>
+      </c>
+      <c r="K1136" t="str">
+        <v>14.507217</v>
+      </c>
+      <c r="L1136" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1136" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1136" t="str">
+        <v/>
+      </c>
+      <c r="O1136" t="str">
+        <v>gourmet food market</v>
+      </c>
+      <c r="P1136" t="str">
+        <v/>
+      </c>
+      <c r="Q1136" t="str">
+        <v/>
+      </c>
+      <c r="R1136" t="str">
+        <v/>
+      </c>
+      <c r="S1136" t="str">
+        <v/>
+      </c>
+      <c r="T1136" t="str">
+        <v/>
+      </c>
+      <c r="U1136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1137" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1137" t="str">
+        <v>Locksmith Alley</v>
+      </c>
+      <c r="D1137" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1137">
+        <v>1</v>
+      </c>
+      <c r="F1137" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1137" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1137" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1137" t="str">
+        <v/>
+      </c>
+      <c r="J1137" t="str">
+        <v>46.049703</v>
+      </c>
+      <c r="K1137" t="str">
+        <v>14.506072</v>
+      </c>
+      <c r="L1137" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1137" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1137" t="str">
+        <v/>
+      </c>
+      <c r="O1137" t="str">
+        <v>Little alley with strange bronze statue faces. Hard to miss if you don't look down!</v>
+      </c>
+      <c r="P1137" t="str">
+        <v/>
+      </c>
+      <c r="Q1137" t="str">
+        <v/>
+      </c>
+      <c r="R1137" t="str">
+        <v/>
+      </c>
+      <c r="S1137" t="str">
+        <v/>
+      </c>
+      <c r="T1137" t="str">
+        <v/>
+      </c>
+      <c r="U1137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1138" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>Stožice Stadium</v>
+      </c>
+      <c r="D1138" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1138">
+        <v>1</v>
+      </c>
+      <c r="F1138" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1138" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1138" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1138" t="str">
+        <v/>
+      </c>
+      <c r="J1138" t="str">
+        <v>46.080462</v>
+      </c>
+      <c r="K1138" t="str">
+        <v>14.524235</v>
+      </c>
+      <c r="L1138" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1138" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1138" t="str">
+        <v/>
+      </c>
+      <c r="O1138" t="str">
+        <v>Went for the Slovenia vs Scotland Nations League game! Walked from the city center and then took the bus back.</v>
+      </c>
+      <c r="P1138" t="str">
+        <v/>
+      </c>
+      <c r="Q1138" t="str">
+        <v/>
+      </c>
+      <c r="R1138" t="str">
+        <v/>
+      </c>
+      <c r="S1138" t="str">
+        <v/>
+      </c>
+      <c r="T1138" t="str">
+        <v/>
+      </c>
+      <c r="U1138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1139" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1139" t="str">
+        <v>Aurora Slaščičarna Ljubljana center</v>
+      </c>
+      <c r="D1139" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E1139" t="str">
+        <v/>
+      </c>
+      <c r="F1139" t="str">
+        <v>🥐</v>
+      </c>
+      <c r="G1139" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1139" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1139" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1139" t="str">
+        <v>46.054636</v>
+      </c>
+      <c r="K1139" t="str">
+        <v>14.507515</v>
+      </c>
+      <c r="L1139" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1139" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1139" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1139" t="str">
+        <v>Large selection of GF baked goods</v>
+      </c>
+      <c r="P1139" t="str">
+        <v>https://www.findmeglutenfree.com/biz/aurora-slascicarna/5623797319598080</v>
+      </c>
+      <c r="Q1139">
+        <v>5</v>
+      </c>
+      <c r="R1139" t="str">
+        <v>[2026-10-09 research] 100% gluten-free dedicated bakery with large selection of GF baked goods. Offers cinnamon rolls, pastries, bread, cookies, mini pizza, bread with sausage. Everything preorder.</v>
+      </c>
+      <c r="S1139" t="str">
+        <v/>
+      </c>
+      <c r="T1139" t="str">
+        <v/>
+      </c>
+      <c r="U1139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1140" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1140" t="str">
+        <v>Glutines</v>
+      </c>
+      <c r="D1140" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E1140">
+        <v>1</v>
+      </c>
+      <c r="F1140" t="str">
+        <v>🥐</v>
+      </c>
+      <c r="G1140" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1140" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1140" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1140" t="str">
+        <v>46.0476</v>
+      </c>
+      <c r="K1140" t="str">
+        <v>14.506363</v>
+      </c>
+      <c r="L1140" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1140" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1140" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1140" t="str">
+        <v>Cheese danish was DELICIOUS. I wish I could go back and get 10 more. They had a ton of other options that looked amazing and I wish I had been able to try them. They also had a large selection of GF snacks and grocery items.</v>
+      </c>
+      <c r="P1140" t="str">
+        <v/>
+      </c>
+      <c r="Q1140">
+        <v>5</v>
+      </c>
+      <c r="R1140" t="str">
+        <v>[2026-10-09 research] 100% dedicated gluten-free bakery with large selection of GF baked goods including cheese danish, pastries, bread, cookies, granola. Small grocery section with pasta, flours, snacks.</v>
+      </c>
+      <c r="S1140" t="str">
+        <v/>
+      </c>
+      <c r="T1140" t="str">
+        <v/>
+      </c>
+      <c r="U1140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1141" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1141" t="str">
+        <v>DA BU DA, Asian Fusion &amp; Bar</v>
+      </c>
+      <c r="D1141" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1141">
+        <v>1</v>
+      </c>
+      <c r="F1141" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1141" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1141" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1141" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1141" t="str">
+        <v>46.050814</v>
+      </c>
+      <c r="K1141" t="str">
+        <v>14.501888</v>
+      </c>
+      <c r="L1141" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1141" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1141" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1141" t="str">
+        <v>Probably shouldn't have eaten here but I was starving and desperate to get something before my bus to Kranjska Gora (that ended up not ever coming). They will use GF soy sauce on the pad thai but do not guarantee no cross contamination. Didn't feel too great afterwards but that could've just been the stress!</v>
+      </c>
+      <c r="P1141" t="str">
+        <v>https://www.findmeglutenfree.com/biz/da-bu-da/5096059852685312</v>
+      </c>
+      <c r="Q1141">
+        <v>2</v>
+      </c>
+      <c r="R1141" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers GF soy sauce for pad thai, fried rice available GF. Friendly staff knowledgeable about GF options. No guaranteed CC prevention.</v>
+      </c>
+      <c r="S1141" t="str">
+        <v/>
+      </c>
+      <c r="T1141" t="str">
+        <v/>
+      </c>
+      <c r="U1141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1142" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1142" t="str">
+        <v>Restavracija Most</v>
+      </c>
+      <c r="D1142" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1142">
+        <v>0</v>
+      </c>
+      <c r="F1142" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1142" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1142" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1142" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1142" t="str">
+        <v>46.052065</v>
+      </c>
+      <c r="K1142" t="str">
+        <v>14.508646</v>
+      </c>
+      <c r="L1142" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1142" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1142" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1142" t="str">
+        <v>Have salads, risotto - upscale but looks very good. Did not get a chance to go.</v>
+      </c>
+      <c r="P1142" t="str">
+        <v>https://www.findmeglutenfree.com/biz/restavracija-most/5414611564232704</v>
+      </c>
+      <c r="Q1142">
+        <v>4</v>
+      </c>
+      <c r="R1142" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers GF risotto, salads, dessert. Allergens marked on menu. Helpful staff. Waiter can advise on GF adaptations.</v>
+      </c>
+      <c r="S1142" t="str">
+        <v/>
+      </c>
+      <c r="T1142" t="str">
+        <v/>
+      </c>
+      <c r="U1142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1143" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1143" t="str">
+        <v>Kranjska Gora P+R</v>
+      </c>
+      <c r="D1143" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1143">
+        <v>1</v>
+      </c>
+      <c r="F1143" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1143" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1143" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1143" t="str">
+        <v/>
+      </c>
+      <c r="J1143" t="str">
+        <v>46.487252</v>
+      </c>
+      <c r="K1143" t="str">
+        <v>13.77809</v>
+      </c>
+      <c r="L1143" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1143" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1143" t="str">
+        <v/>
+      </c>
+      <c r="O1143" t="str">
+        <v>Catch the shuttle/bus to Vrsic Pass (runs until Sept 30th only!)</v>
+      </c>
+      <c r="P1143" t="str">
+        <v/>
+      </c>
+      <c r="Q1143" t="str">
+        <v/>
+      </c>
+      <c r="R1143" t="str">
+        <v/>
+      </c>
+      <c r="S1143" t="str">
+        <v/>
+      </c>
+      <c r="T1143" t="str">
+        <v/>
+      </c>
+      <c r="U1143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1144" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1144" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="D1144" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1144">
+        <v>1</v>
+      </c>
+      <c r="F1144" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1144" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1144" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1144" t="str">
+        <v/>
+      </c>
+      <c r="J1144" t="str">
+        <v>46.486919</v>
+      </c>
+      <c r="K1144" t="str">
+        <v>13.786767</v>
+      </c>
+      <c r="L1144" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1144" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1144" t="str">
+        <v/>
+      </c>
+      <c r="O1144" t="str">
+        <v/>
+      </c>
+      <c r="P1144" t="str">
+        <v/>
+      </c>
+      <c r="Q1144" t="str">
+        <v/>
+      </c>
+      <c r="R1144" t="str">
+        <v/>
+      </c>
+      <c r="S1144" t="str">
+        <v>https://www.hotels.com/ho3198304064/</v>
+      </c>
+      <c r="T1144" t="str">
+        <v/>
+      </c>
+      <c r="U1144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1145" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1145" t="str">
+        <v>Kranjska Gora Jasna</v>
+      </c>
+      <c r="D1145" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1145" t="str">
+        <v/>
+      </c>
+      <c r="F1145" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1145" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1145" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1145" t="str">
+        <v/>
+      </c>
+      <c r="J1145" t="str">
+        <v>46.474992</v>
+      </c>
+      <c r="K1145" t="str">
+        <v>13.784721</v>
+      </c>
+      <c r="L1145" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1145" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1145" t="str">
+        <v/>
+      </c>
+      <c r="O1145" t="str">
+        <v/>
+      </c>
+      <c r="P1145" t="str">
+        <v/>
+      </c>
+      <c r="Q1145" t="str">
+        <v/>
+      </c>
+      <c r="R1145" t="str">
+        <v/>
+      </c>
+      <c r="S1145" t="str">
+        <v/>
+      </c>
+      <c r="T1145" t="str">
+        <v/>
+      </c>
+      <c r="U1145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1146" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1146" t="str">
+        <v>Vršič</v>
+      </c>
+      <c r="D1146" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1146">
+        <v>1</v>
+      </c>
+      <c r="F1146" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1146" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1146" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1146" t="str">
+        <v/>
+      </c>
+      <c r="J1146" t="str">
+        <v>46.434606</v>
+      </c>
+      <c r="K1146" t="str">
+        <v>13.743614</v>
+      </c>
+      <c r="L1146" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1146" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1146" t="str">
+        <v/>
+      </c>
+      <c r="O1146" t="str">
+        <v/>
+      </c>
+      <c r="P1146" t="str">
+        <v/>
+      </c>
+      <c r="Q1146" t="str">
+        <v/>
+      </c>
+      <c r="R1146" t="str">
+        <v/>
+      </c>
+      <c r="S1146" t="str">
+        <v/>
+      </c>
+      <c r="T1146" t="str">
+        <v/>
+      </c>
+      <c r="U1146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1147" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1147" t="str">
+        <v>Vrsic Pass Parking</v>
+      </c>
+      <c r="D1147" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1147">
+        <v>1</v>
+      </c>
+      <c r="F1147" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1147" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1147" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1147" t="str">
+        <v/>
+      </c>
+      <c r="J1147" t="str">
+        <v>46.433394</v>
+      </c>
+      <c r="K1147" t="str">
+        <v>13.743559</v>
+      </c>
+      <c r="L1147" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1147" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1147" t="str">
+        <v/>
+      </c>
+      <c r="O1147" t="str">
+        <v>Start of Sleme hike I think?</v>
+      </c>
+      <c r="P1147" t="str">
+        <v/>
+      </c>
+      <c r="Q1147" t="str">
+        <v/>
+      </c>
+      <c r="R1147" t="str">
+        <v/>
+      </c>
+      <c r="S1147" t="str">
+        <v/>
+      </c>
+      <c r="T1147" t="str">
+        <v/>
+      </c>
+      <c r="U1147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1148" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1148" t="str">
+        <v>Boutique Hotel Skipass</v>
+      </c>
+      <c r="D1148" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1148">
+        <v>1</v>
+      </c>
+      <c r="F1148" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1148" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1148" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1148" t="str">
+        <v/>
+      </c>
+      <c r="J1148" t="str">
+        <v>46.487304</v>
+      </c>
+      <c r="K1148" t="str">
+        <v>13.787067</v>
+      </c>
+      <c r="L1148" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1148" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1148" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1148" t="str">
+        <v>Where I stayed! Double room with a balcony and a view of the mountains. It's literally right next to the bus stop. The breakfast was incredible! They offer an a la carte menu for you to choose from and had gluten free bread available for me. The yogurt bowl with fruit (I got it with no granola) was beautiful. All of the staff were SO SO nice - like beyond nice. And the wellness room was great. You have to book it so that you can enjoy it privately but there are two saunas - infrared and finnish - showers, lounge beds, tea, etc. If you're headed to Kranjska Gora from Ljubljana, don't make the same mistake I did and take the last bus of the day. I ended up having to call an uber and it cost ~105 euros or so. There is no way to track where the buses are unfortunately, so I waited 30 minutes past the time it was meant to be there and ended up getting into Kranjska Gora well past dark.</v>
+      </c>
+      <c r="P1148" t="str">
+        <v/>
+      </c>
+      <c r="Q1148" t="str">
+        <v/>
+      </c>
+      <c r="R1148" t="str">
+        <v/>
+      </c>
+      <c r="S1148" t="str">
+        <v>https://www.hotels.com/ho1191823040/botique-hotel-skipass-kranjska-gora-slovenia/</v>
+      </c>
+      <c r="T1148" t="str">
+        <v/>
+      </c>
+      <c r="U1148" t="str">
+        <v>A la carte breakfast menu with gluten-free bread available.</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1149" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1149" t="str">
+        <v>Boutique Hotel Milka</v>
+      </c>
+      <c r="D1149" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1149">
+        <v>0</v>
+      </c>
+      <c r="F1149" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1149" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1149" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1149" t="str">
+        <v/>
+      </c>
+      <c r="J1149" t="str">
+        <v>46.475129</v>
+      </c>
+      <c r="K1149" t="str">
+        <v>13.784806</v>
+      </c>
+      <c r="L1149" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1149" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1149" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1149" t="str">
+        <v>Where I wanted to stay - looks so upscale and nice in nature and secluded. But sold out on one of the dates I was there. Was a blessing in disguise because I LOVED hotel skipass.</v>
+      </c>
+      <c r="P1149" t="str">
+        <v/>
+      </c>
+      <c r="Q1149" t="str">
+        <v/>
+      </c>
+      <c r="R1149" t="str">
+        <v/>
+      </c>
+      <c r="S1149" t="str">
+        <v>https://www.hotels.com/ho1047885856/pension-milka-kranjska-gora-slovenia/</v>
+      </c>
+      <c r="T1149" t="str">
+        <v/>
+      </c>
+      <c r="U1149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1150" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1150" t="str">
+        <v>Triangel Boutique Hotel</v>
+      </c>
+      <c r="D1150" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1150">
+        <v>0</v>
+      </c>
+      <c r="F1150" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1150" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1150" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1150" t="str">
+        <v/>
+      </c>
+      <c r="J1150" t="str">
+        <v>46.482176</v>
+      </c>
+      <c r="K1150" t="str">
+        <v>13.837516</v>
+      </c>
+      <c r="L1150" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1150" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1150" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1150" t="str">
+        <v>Looks nice but too far from town</v>
+      </c>
+      <c r="P1150" t="str">
+        <v/>
+      </c>
+      <c r="Q1150" t="str">
+        <v/>
+      </c>
+      <c r="R1150" t="str">
+        <v/>
+      </c>
+      <c r="S1150" t="str">
+        <v>https://www.hotels.com/ho2946370656/triangel-boutique-hotel-kranjska-gora-slovenia/</v>
+      </c>
+      <c r="T1150" t="str">
+        <v/>
+      </c>
+      <c r="U1150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1151" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1151" t="str">
+        <v>Hotel Kranjska Gora</v>
+      </c>
+      <c r="D1151" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1151">
+        <v>0</v>
+      </c>
+      <c r="F1151" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1151" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1151" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1151" t="str">
+        <v/>
+      </c>
+      <c r="J1151" t="str">
+        <v>46.481554</v>
+      </c>
+      <c r="K1151" t="str">
+        <v>13.781512</v>
+      </c>
+      <c r="L1151" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1151" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1151" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1151" t="str">
+        <v>Looks nice but wanted to stay closer to town &amp; a bus stop. But is in a good location near Lake Jasna.</v>
+      </c>
+      <c r="P1151" t="str">
+        <v/>
+      </c>
+      <c r="Q1151" t="str">
+        <v/>
+      </c>
+      <c r="R1151" t="str">
+        <v/>
+      </c>
+      <c r="S1151" t="str">
+        <v/>
+      </c>
+      <c r="T1151" t="str">
+        <v/>
+      </c>
+      <c r="U1151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1152" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1152" t="str">
+        <v>Sleme</v>
+      </c>
+      <c r="D1152" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1152">
+        <v>1</v>
+      </c>
+      <c r="F1152" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1152" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1152" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1152" t="str">
+        <v/>
+      </c>
+      <c r="J1152" t="str">
+        <v>46.451667</v>
+      </c>
+      <c r="K1152" t="str">
+        <v>13.871667</v>
+      </c>
+      <c r="L1152" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1152" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1152" t="str">
+        <v/>
+      </c>
+      <c r="O1152" t="str">
+        <v>Ride the bus down to Vrsic Pass (I don't know how the bus drivers manage those turns! It's crazy) and then you'll find the signs. Very clearly marked hike and trail. There's a little souvenir shop with waters and sodas nearby the parking lot/bus stop and a mountain hut up the way, but it was closed.</v>
+      </c>
+      <c r="P1152" t="str">
+        <v/>
+      </c>
+      <c r="Q1152" t="str">
+        <v/>
+      </c>
+      <c r="R1152" t="str">
+        <v/>
+      </c>
+      <c r="S1152" t="str">
+        <v/>
+      </c>
+      <c r="T1152" t="str">
+        <v/>
+      </c>
+      <c r="U1152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1153" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1153" t="str">
+        <v>Vršič Pass</v>
+      </c>
+      <c r="D1153" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1153">
+        <v>1</v>
+      </c>
+      <c r="F1153" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1153" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1153" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1153" t="str">
+        <v/>
+      </c>
+      <c r="J1153" t="str">
+        <v>46.432897</v>
+      </c>
+      <c r="K1153" t="str">
+        <v>13.743071</v>
+      </c>
+      <c r="L1153" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1153" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1153" t="str">
+        <v/>
+      </c>
+      <c r="O1153" t="str">
+        <v/>
+      </c>
+      <c r="P1153" t="str">
+        <v/>
+      </c>
+      <c r="Q1153" t="str">
+        <v/>
+      </c>
+      <c r="R1153" t="str">
+        <v/>
+      </c>
+      <c r="S1153" t="str">
+        <v/>
+      </c>
+      <c r="T1153" t="str">
+        <v/>
+      </c>
+      <c r="U1153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1154" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1154" t="str">
+        <v>Lake Jasna</v>
+      </c>
+      <c r="D1154" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1154">
+        <v>1</v>
+      </c>
+      <c r="F1154" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1154" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1154" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1154" t="str">
+        <v/>
+      </c>
+      <c r="J1154" t="str">
+        <v>46.474042</v>
+      </c>
+      <c r="K1154" t="str">
+        <v>13.784095</v>
+      </c>
+      <c r="L1154" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1154" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1154" t="str">
+        <v/>
+      </c>
+      <c r="O1154" t="str">
+        <v>Gorgeous lake (but small) - must go and walk around both sides - it won't take you too long.</v>
+      </c>
+      <c r="P1154" t="str">
+        <v/>
+      </c>
+      <c r="Q1154" t="str">
+        <v/>
+      </c>
+      <c r="R1154" t="str">
+        <v/>
+      </c>
+      <c r="S1154" t="str">
+        <v/>
+      </c>
+      <c r="T1154" t="str">
+        <v/>
+      </c>
+      <c r="U1154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1155" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1155" t="str">
+        <v>Zelenci Nature Reserve</v>
+      </c>
+      <c r="D1155" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1155">
+        <v>0</v>
+      </c>
+      <c r="F1155" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1155" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1155" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1155" t="str">
+        <v/>
+      </c>
+      <c r="J1155" t="str">
+        <v>46.492576</v>
+      </c>
+      <c r="K1155" t="str">
+        <v>13.737759</v>
+      </c>
+      <c r="L1155" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1155" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1155" t="str">
+        <v/>
+      </c>
+      <c r="O1155" t="str">
+        <v>Didn't make it here, but looked like a fun place to rent a bike in Kranjska Gora and bike there!</v>
+      </c>
+      <c r="P1155" t="str">
+        <v/>
+      </c>
+      <c r="Q1155" t="str">
+        <v/>
+      </c>
+      <c r="R1155" t="str">
+        <v/>
+      </c>
+      <c r="S1155" t="str">
+        <v/>
+      </c>
+      <c r="T1155" t="str">
+        <v/>
+      </c>
+      <c r="U1155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1156" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1156" t="str">
+        <v>Mala Mojstrovka</v>
+      </c>
+      <c r="D1156" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1156">
+        <v>0</v>
+      </c>
+      <c r="F1156" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1156" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1156" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1156" t="str">
+        <v/>
+      </c>
+      <c r="J1156" t="str">
+        <v>46.43735</v>
+      </c>
+      <c r="K1156" t="str">
+        <v>13.731188</v>
+      </c>
+      <c r="L1156" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1156" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1156" t="str">
+        <v/>
+      </c>
+      <c r="O1156" t="str">
+        <v>Didn't do this hike....but sounds like you need to hike from the south side, otherwise it's climbing and via ferratas.</v>
+      </c>
+      <c r="P1156" t="str">
+        <v/>
+      </c>
+      <c r="Q1156" t="str">
+        <v/>
+      </c>
+      <c r="R1156" t="str">
+        <v/>
+      </c>
+      <c r="S1156" t="str">
+        <v/>
+      </c>
+      <c r="T1156" t="str">
+        <v/>
+      </c>
+      <c r="U1156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1157" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1157" t="str">
+        <v>Ławka Kranjska Gora</v>
+      </c>
+      <c r="D1157" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1157" t="str">
+        <v/>
+      </c>
+      <c r="F1157" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1157" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1157" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1157" t="str">
+        <v/>
+      </c>
+      <c r="J1157" t="str">
+        <v>46.474556</v>
+      </c>
+      <c r="K1157" t="str">
+        <v>13.784085</v>
+      </c>
+      <c r="L1157" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1157" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1157" t="str">
+        <v/>
+      </c>
+      <c r="O1157" t="str">
+        <v/>
+      </c>
+      <c r="P1157" t="str">
+        <v/>
+      </c>
+      <c r="Q1157" t="str">
+        <v/>
+      </c>
+      <c r="R1157" t="str">
+        <v/>
+      </c>
+      <c r="S1157" t="str">
+        <v/>
+      </c>
+      <c r="T1157" t="str">
+        <v/>
+      </c>
+      <c r="U1157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1158" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1158" t="str">
+        <v>Na Malo Mojstrovko po plezalni poti</v>
+      </c>
+      <c r="D1158" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1158">
+        <v>0</v>
+      </c>
+      <c r="F1158" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1158" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1158" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1158" t="str">
+        <v/>
+      </c>
+      <c r="J1158" t="str">
+        <v>46.435339</v>
+      </c>
+      <c r="K1158" t="str">
+        <v>13.744077</v>
+      </c>
+      <c r="L1158" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1158" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1158" t="str">
+        <v/>
+      </c>
+      <c r="O1158" t="str">
+        <v>Didn't end up making it here.</v>
+      </c>
+      <c r="P1158" t="str">
+        <v/>
+      </c>
+      <c r="Q1158" t="str">
+        <v/>
+      </c>
+      <c r="R1158" t="str">
+        <v/>
+      </c>
+      <c r="S1158" t="str">
+        <v/>
+      </c>
+      <c r="T1158" t="str">
+        <v/>
+      </c>
+      <c r="U1158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1159" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1159" t="str">
+        <v>Vršič</v>
+      </c>
+      <c r="D1159" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1159" t="str">
+        <v/>
+      </c>
+      <c r="F1159" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1159" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1159" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1159" t="str">
+        <v/>
+      </c>
+      <c r="J1159" t="str">
+        <v>46.434083</v>
+      </c>
+      <c r="K1159" t="str">
+        <v>13.746686</v>
+      </c>
+      <c r="L1159" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1159" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1159" t="str">
+        <v/>
+      </c>
+      <c r="O1159" t="str">
+        <v/>
+      </c>
+      <c r="P1159" t="str">
+        <v/>
+      </c>
+      <c r="Q1159" t="str">
+        <v/>
+      </c>
+      <c r="R1159" t="str">
+        <v/>
+      </c>
+      <c r="S1159" t="str">
+        <v/>
+      </c>
+      <c r="T1159" t="str">
+        <v/>
+      </c>
+      <c r="U1159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1160" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1160" t="str">
+        <v>Restaurant Oštarija</v>
+      </c>
+      <c r="D1160" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1160">
+        <v>1</v>
+      </c>
+      <c r="F1160" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1160" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1160" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1160" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1160" t="str">
+        <v>46.485436</v>
+      </c>
+      <c r="K1160" t="str">
+        <v>13.778785</v>
+      </c>
+      <c r="L1160" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1160" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1160" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1160" t="str">
+        <v>Ate here twice. Asked if the mushroom risotto was GF (a FMGF review suggested it might be). The waiter came back and said it was not but that the chef could make me truffle risotto. The truffle risotto was AMAZING and the views and atmosphere outside were great. I ended up going back to have the truffle risotto (not actually on the menu but I explained they made it GF for me the day before) again.</v>
+      </c>
+      <c r="P1160" t="str">
+        <v>https://www.findmeglutenfree.com/biz/ostarija/4982086303350784</v>
+      </c>
+      <c r="Q1160">
+        <v>4</v>
+      </c>
+      <c r="R1160" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Has gluten-free menu. Staff friendly and knowledgeable about GF options. GF truffle risotto made off-menu. Seafood and dessert on GF menu.</v>
+      </c>
+      <c r="S1160" t="str">
+        <v/>
+      </c>
+      <c r="T1160" t="str">
+        <v/>
+      </c>
+      <c r="U1160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1161" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1161" t="str">
+        <v>Pri Martinu</v>
+      </c>
+      <c r="D1161" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1161">
+        <v>0</v>
+      </c>
+      <c r="F1161" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1161" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1161" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1161" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1161" t="str">
+        <v>46.485559</v>
+      </c>
+      <c r="K1161" t="str">
+        <v>13.78798</v>
+      </c>
+      <c r="L1161" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1161" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1161" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1161" t="str">
+        <v>Did not end up eating here.</v>
+      </c>
+      <c r="P1161" t="str">
+        <v/>
+      </c>
+      <c r="Q1161">
+        <v>2</v>
+      </c>
+      <c r="R1161" t="str">
+        <v/>
+      </c>
+      <c r="S1161" t="str">
+        <v/>
+      </c>
+      <c r="T1161" t="str">
+        <v/>
+      </c>
+      <c r="U1161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1162" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="C1162" t="str">
+        <v>Restaurant Milka</v>
+      </c>
+      <c r="D1162" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1162">
+        <v>0</v>
+      </c>
+      <c r="F1162" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1162" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1162" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1162" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1162" t="str">
+        <v>46.475143</v>
+      </c>
+      <c r="K1162" t="str">
+        <v>13.78479</v>
+      </c>
+      <c r="L1162" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1162" t="str">
+        <v>Kranjska Gora</v>
+      </c>
+      <c r="N1162" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1162" t="str">
+        <v>Said GF is possible but may be cross contamination - could not eat here during my stay as it was closed Sun, Mon, &amp; Tues and I did not arrive until late Sat night.</v>
+      </c>
+      <c r="P1162" t="str">
+        <v/>
+      </c>
+      <c r="Q1162">
+        <v>3</v>
+      </c>
+      <c r="R1162" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Has gluten-free menu. Staff friendly and knowledgeable about GF options. GF truffle risotto made off-menu. Seafood and dessert on GF menu.</v>
+      </c>
+      <c r="S1162" t="str">
+        <v/>
+      </c>
+      <c r="T1162" t="str">
+        <v/>
+      </c>
+      <c r="U1162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1163" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1163" t="str">
+        <v>Hotel Soča</v>
+      </c>
+      <c r="D1163" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1163">
+        <v>1</v>
+      </c>
+      <c r="F1163" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1163" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1163" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1163" t="str">
+        <v/>
+      </c>
+      <c r="J1163" t="str">
+        <v>46.33806</v>
+      </c>
+      <c r="K1163" t="str">
+        <v>13.555046</v>
+      </c>
+      <c r="L1163" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1163" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1163" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1163" t="str">
+        <v>Was a very nice hotel in a good location. Would stay there again. Breakfast was good too with plenty of GF options in the buffet like scrambled eggs, smoked salmon, hard boiled eggs, etc.</v>
+      </c>
+      <c r="P1163" t="str">
+        <v/>
+      </c>
+      <c r="Q1163" t="str">
+        <v/>
+      </c>
+      <c r="R1163" t="str">
+        <v/>
+      </c>
+      <c r="S1163" t="str">
+        <v>https://www.hotelsoca.si/en/hotel/</v>
+      </c>
+      <c r="T1163" t="str">
+        <v/>
+      </c>
+      <c r="U1163" t="str">
+        <v>Breakfast buffet with plenty of naturally GF options (scrambled eggs, smoked salmon, hard-boiled eggs).</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1164" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1164" t="str">
+        <v>Lepena K</v>
+      </c>
+      <c r="D1164" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1164" t="str">
+        <v/>
+      </c>
+      <c r="F1164" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1164" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1164" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1164" t="str">
+        <v/>
+      </c>
+      <c r="J1164" t="str">
+        <v>46.338086</v>
+      </c>
+      <c r="K1164" t="str">
+        <v>13.64568</v>
+      </c>
+      <c r="L1164" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1164" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1164" t="str">
+        <v/>
+      </c>
+      <c r="O1164" t="str">
+        <v/>
+      </c>
+      <c r="P1164" t="str">
+        <v/>
+      </c>
+      <c r="Q1164" t="str">
+        <v/>
+      </c>
+      <c r="R1164" t="str">
+        <v/>
+      </c>
+      <c r="S1164" t="str">
+        <v/>
+      </c>
+      <c r="T1164" t="str">
+        <v/>
+      </c>
+      <c r="U1164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1165" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1165" t="str">
+        <v>Soča</v>
+      </c>
+      <c r="D1165" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1165" t="str">
+        <v/>
+      </c>
+      <c r="F1165" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1165" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1165" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1165" t="str">
+        <v/>
+      </c>
+      <c r="J1165" t="str">
+        <v>46.34188</v>
+      </c>
+      <c r="K1165" t="str">
+        <v>13.666573</v>
+      </c>
+      <c r="L1165" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1165" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1165" t="str">
+        <v/>
+      </c>
+      <c r="O1165" t="str">
+        <v/>
+      </c>
+      <c r="P1165" t="str">
+        <v/>
+      </c>
+      <c r="Q1165" t="str">
+        <v/>
+      </c>
+      <c r="R1165" t="str">
+        <v/>
+      </c>
+      <c r="S1165" t="str">
+        <v/>
+      </c>
+      <c r="T1165" t="str">
+        <v/>
+      </c>
+      <c r="U1165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1166" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1166" t="str">
+        <v>Izvir Soče K</v>
+      </c>
+      <c r="D1166" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1166" t="str">
+        <v/>
+      </c>
+      <c r="F1166" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1166" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1166" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1166" t="str">
+        <v/>
+      </c>
+      <c r="J1166" t="str">
+        <v>46.405954</v>
+      </c>
+      <c r="K1166" t="str">
+        <v>13.739555</v>
+      </c>
+      <c r="L1166" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1166" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1166" t="str">
+        <v/>
+      </c>
+      <c r="O1166" t="str">
+        <v/>
+      </c>
+      <c r="P1166" t="str">
+        <v/>
+      </c>
+      <c r="Q1166" t="str">
+        <v/>
+      </c>
+      <c r="R1166" t="str">
+        <v/>
+      </c>
+      <c r="S1166" t="str">
+        <v/>
+      </c>
+      <c r="T1166" t="str">
+        <v/>
+      </c>
+      <c r="U1166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1167" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1167" t="str">
+        <v>ZIPLINE SLOVENIA, Adrenalin Park Bovec</v>
+      </c>
+      <c r="D1167" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1167">
+        <v>1</v>
+      </c>
+      <c r="F1167" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1167" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1167" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1167" t="str">
+        <v/>
+      </c>
+      <c r="J1167" t="str">
+        <v>46.338245</v>
+      </c>
+      <c r="K1167" t="str">
+        <v>13.55251</v>
+      </c>
+      <c r="L1167" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1167" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1167" t="str">
+        <v/>
+      </c>
+      <c r="O1167" t="str">
+        <v>Did the zipline with Soča Rafting (booked through Hotel Soča). The views were gorgeous. Would highly recommend. (Kelly confirmed 2026-10-09 it was Soča Rafting, not Zipline Slovenia.)</v>
+      </c>
+      <c r="P1167" t="str">
+        <v/>
+      </c>
+      <c r="Q1167" t="str">
+        <v/>
+      </c>
+      <c r="R1167" t="str">
+        <v/>
+      </c>
+      <c r="S1167" t="str">
+        <v/>
+      </c>
+      <c r="T1167" t="str">
+        <v/>
+      </c>
+      <c r="U1167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1168" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1168" t="str">
+        <v>Great Soča Gorge</v>
+      </c>
+      <c r="D1168" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1168">
+        <v>1</v>
+      </c>
+      <c r="F1168" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1168" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1168" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1168" t="str">
+        <v/>
+      </c>
+      <c r="J1168" t="str">
+        <v>46.33721</v>
+      </c>
+      <c r="K1168" t="str">
+        <v>13.645934</v>
+      </c>
+      <c r="L1168" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1168" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1168" t="str">
+        <v/>
+      </c>
+      <c r="O1168" t="str">
+        <v>Stopped here as a was walking the Soca Trail. Absolutely beautiful but was definitely more crowded than most places (even in tourist offseason). Must visit though!</v>
+      </c>
+      <c r="P1168" t="str">
+        <v/>
+      </c>
+      <c r="Q1168" t="str">
+        <v/>
+      </c>
+      <c r="R1168" t="str">
+        <v/>
+      </c>
+      <c r="S1168" t="str">
+        <v/>
+      </c>
+      <c r="T1168" t="str">
+        <v/>
+      </c>
+      <c r="U1168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1169" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1169" t="str">
+        <v>Slap Virje</v>
+      </c>
+      <c r="D1169" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1169">
+        <v>0</v>
+      </c>
+      <c r="F1169" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1169" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1169" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1169" t="str">
+        <v/>
+      </c>
+      <c r="J1169" t="str">
+        <v>46.335119</v>
+      </c>
+      <c r="K1169" t="str">
+        <v>13.514208</v>
+      </c>
+      <c r="L1169" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1169" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1169" t="str">
+        <v/>
+      </c>
+      <c r="O1169" t="str">
+        <v>Didn't venture over here.</v>
+      </c>
+      <c r="P1169" t="str">
+        <v/>
+      </c>
+      <c r="Q1169" t="str">
+        <v/>
+      </c>
+      <c r="R1169" t="str">
+        <v/>
+      </c>
+      <c r="S1169" t="str">
+        <v/>
+      </c>
+      <c r="T1169" t="str">
+        <v/>
+      </c>
+      <c r="U1169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1170" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1170" t="str">
+        <v>Boka Waterfall</v>
+      </c>
+      <c r="D1170" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1170">
+        <v>1</v>
+      </c>
+      <c r="F1170" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1170" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1170" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1170" t="str">
+        <v/>
+      </c>
+      <c r="J1170" t="str">
+        <v>46.321426</v>
+      </c>
+      <c r="K1170" t="str">
+        <v>13.482004</v>
+      </c>
+      <c r="L1170" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1170" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1170" t="str">
+        <v/>
+      </c>
+      <c r="O1170" t="str">
+        <v>Apparently the largest waterfall in Slovenia. However, it was sadly pretty dried up at the time I went.</v>
+      </c>
+      <c r="P1170" t="str">
+        <v/>
+      </c>
+      <c r="Q1170" t="str">
+        <v/>
+      </c>
+      <c r="R1170" t="str">
+        <v/>
+      </c>
+      <c r="S1170" t="str">
+        <v/>
+      </c>
+      <c r="T1170" t="str">
+        <v/>
+      </c>
+      <c r="U1170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1171" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1171" t="str">
+        <v>Krn</v>
+      </c>
+      <c r="D1171" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1171">
+        <v>0</v>
+      </c>
+      <c r="F1171" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1171" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1171" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1171" t="str">
+        <v/>
+      </c>
+      <c r="J1171" t="str">
+        <v>46.266111</v>
+      </c>
+      <c r="K1171" t="str">
+        <v>13.658333</v>
+      </c>
+      <c r="L1171" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1171" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1171" t="str">
+        <v/>
+      </c>
+      <c r="O1171" t="str">
+        <v>Didn't get a chance to do this hike.</v>
+      </c>
+      <c r="P1171" t="str">
+        <v/>
+      </c>
+      <c r="Q1171" t="str">
+        <v/>
+      </c>
+      <c r="R1171" t="str">
+        <v/>
+      </c>
+      <c r="S1171" t="str">
+        <v/>
+      </c>
+      <c r="T1171" t="str">
+        <v/>
+      </c>
+      <c r="U1171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1172" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1172" t="str">
+        <v>Alpine Pasture Kuhinja</v>
+      </c>
+      <c r="D1172" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1172">
+        <v>0</v>
+      </c>
+      <c r="F1172" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1172" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1172" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1172" t="str">
+        <v/>
+      </c>
+      <c r="J1172" t="str">
+        <v>46.243287</v>
+      </c>
+      <c r="K1172" t="str">
+        <v>13.662769</v>
+      </c>
+      <c r="L1172" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1172" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1172" t="str">
+        <v/>
+      </c>
+      <c r="O1172" t="str">
+        <v>Didn't get a chance to go here (the bus schedule is a little tough in the offseason), but looks beautiful.</v>
+      </c>
+      <c r="P1172" t="str">
+        <v/>
+      </c>
+      <c r="Q1172" t="str">
+        <v/>
+      </c>
+      <c r="R1172" t="str">
+        <v/>
+      </c>
+      <c r="S1172" t="str">
+        <v/>
+      </c>
+      <c r="T1172" t="str">
+        <v/>
+      </c>
+      <c r="U1172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1173" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1173" t="str">
+        <v>Fratarica</v>
+      </c>
+      <c r="D1173" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1173">
+        <v>0</v>
+      </c>
+      <c r="F1173" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1173" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1173" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1173" t="str">
+        <v/>
+      </c>
+      <c r="J1173" t="str">
+        <v>46.401515</v>
+      </c>
+      <c r="K1173" t="str">
+        <v>13.611149</v>
+      </c>
+      <c r="L1173" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1173" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1173" t="str">
+        <v/>
+      </c>
+      <c r="O1173" t="str">
+        <v>Booked canyoneering through the hotel but it got cancelled since I was the only one who signed up :(</v>
+      </c>
+      <c r="P1173" t="str">
+        <v/>
+      </c>
+      <c r="Q1173" t="str">
+        <v/>
+      </c>
+      <c r="R1173" t="str">
+        <v/>
+      </c>
+      <c r="S1173" t="str">
+        <v/>
+      </c>
+      <c r="T1173" t="str">
+        <v/>
+      </c>
+      <c r="U1173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1174" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1174" t="str">
+        <v>Izvir Soče</v>
+      </c>
+      <c r="D1174" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1174">
+        <v>1</v>
+      </c>
+      <c r="F1174" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1174" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1174" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1174" t="str">
+        <v/>
+      </c>
+      <c r="J1174" t="str">
+        <v>46.411681</v>
+      </c>
+      <c r="K1174" t="str">
+        <v>13.724123</v>
+      </c>
+      <c r="L1174" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1174" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1174" t="str">
+        <v/>
+      </c>
+      <c r="O1174" t="str">
+        <v>Start of the Soca Trail. I did NOT start from here since I had to get back to the hotel by ~3pm for a work meeting. Instead I took the 6:30am bus from Bovec to the Trenta visitor center and started from there. Apparently that segment is the most beautiful part of the hike anyways and it was GORGEOUS and so peaceful. I was the only person on the trail for most of the hike - until I got closer to the Great Soca Gorge).</v>
+      </c>
+      <c r="P1174" t="str">
+        <v/>
+      </c>
+      <c r="Q1174" t="str">
+        <v/>
+      </c>
+      <c r="R1174" t="str">
+        <v/>
+      </c>
+      <c r="S1174" t="str">
+        <v/>
+      </c>
+      <c r="T1174" t="str">
+        <v/>
+      </c>
+      <c r="U1174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1175" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1175" t="str">
+        <v>Hiša Franko</v>
+      </c>
+      <c r="D1175" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1175">
+        <v>0</v>
+      </c>
+      <c r="F1175" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1175" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1175" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1175" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1175" t="str">
+        <v>46.247249</v>
+      </c>
+      <c r="K1175" t="str">
+        <v>13.537761</v>
+      </c>
+      <c r="L1175" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1175" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1175" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1175" t="str">
+        <v>Michelin star restaurant with a lunch and dinner tasting menu. Couldn't make it work to visit this time but maybe next time. Looks incredible!</v>
+      </c>
+      <c r="P1175" t="str">
+        <v/>
+      </c>
+      <c r="Q1175">
+        <v>3</v>
+      </c>
+      <c r="R1175" t="str">
+        <v>[2026-10-09 research] Three Michelin stars. Can accommodate gluten-free with advance notice (1 week minimum). Menu features wild herbs, mountain dairy, river trout, game, mushrooms. Traces may be present; GF not primary focus.</v>
+      </c>
+      <c r="S1175" t="str">
+        <v/>
+      </c>
+      <c r="T1175" t="str">
+        <v/>
+      </c>
+      <c r="U1175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1176" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1176" t="str">
+        <v>Felix</v>
+      </c>
+      <c r="D1176" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1176">
+        <v>1</v>
+      </c>
+      <c r="F1176" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1176" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1176" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1176" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1176" t="str">
+        <v>46.339564</v>
+      </c>
+      <c r="K1176" t="str">
+        <v>13.555385</v>
+      </c>
+      <c r="L1176" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1176" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1176" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1176" t="str">
+        <v>So good I went here twice in two days! The vegetarian burger is GF if you get the GF bun and it was DELICIOUS! I don’t know what’s in the magical sauce they put on it but it’s to die for. The fries are GF as well (garlic parm ones too) and fried in a fryer with no gluten. Ask for the burger sauce as a side to dip your fries - it’s sooo good. One of my favorite meals in Slovenia! Will definitely be back if I’m in the Soca Valley again. Didn't get a chance to try the GF tiramisu (was too full) but I bet it's good!</v>
+      </c>
+      <c r="P1176" t="str">
+        <v>https://www.findmeglutenfree.com/biz/felix/6169534714740736</v>
+      </c>
+      <c r="Q1176">
+        <v>5</v>
+      </c>
+      <c r="R1176" t="str">
+        <v>[2026-10-09 research] Not dedicated GF but has gluten-free menu. Offers GF bun for veggie burger, fries cooked in dedicated GF fryer, GF tiramisu and brownies. Very knowledgeable staff.</v>
+      </c>
+      <c r="S1176" t="str">
+        <v/>
+      </c>
+      <c r="T1176" t="str">
+        <v/>
+      </c>
+      <c r="U1176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1177" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1177" t="str">
+        <v>Sladoledna hiška Janko in Metka</v>
+      </c>
+      <c r="D1177" t="str">
+        <v>cafe</v>
+      </c>
+      <c r="E1177">
+        <v>0</v>
+      </c>
+      <c r="F1177" t="str">
+        <v>☕</v>
+      </c>
+      <c r="G1177" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1177" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1177" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1177" t="str">
+        <v>46.247498</v>
+      </c>
+      <c r="K1177" t="str">
+        <v>13.579416</v>
+      </c>
+      <c r="L1177" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1177" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1177" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1177" t="str">
+        <v>Didn't go.</v>
+      </c>
+      <c r="P1177" t="str">
+        <v/>
+      </c>
+      <c r="Q1177">
+        <v>2</v>
+      </c>
+      <c r="R1177" t="str">
+        <v>[2026-10-09 research] Self-service ice cream shop with homemade ice cream from fresh mountain milk. Offers gluten-free ice cream. Variety of toppings available.</v>
+      </c>
+      <c r="S1177" t="str">
+        <v/>
+      </c>
+      <c r="T1177" t="str">
+        <v/>
+      </c>
+      <c r="U1177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1178" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1178" t="str">
+        <v>Hisa Polonka</v>
+      </c>
+      <c r="D1178" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1178">
+        <v>0</v>
+      </c>
+      <c r="F1178" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1178" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1178" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1178" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1178" t="str">
+        <v>46.247799</v>
+      </c>
+      <c r="K1178" t="str">
+        <v>13.579674</v>
+      </c>
+      <c r="L1178" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1178" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1178" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1178" t="str">
+        <v>Seems to have GF options but is meat-based with traditional Slovenian food (lamb). Didn't go.</v>
+      </c>
+      <c r="P1178" t="str">
+        <v/>
+      </c>
+      <c r="Q1178">
+        <v>3</v>
+      </c>
+      <c r="R1178" t="str">
+        <v/>
+      </c>
+      <c r="S1178" t="str">
+        <v/>
+      </c>
+      <c r="T1178" t="str">
+        <v/>
+      </c>
+      <c r="U1178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1179" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1179" t="str">
+        <v>Pizzeria Kingpizza</v>
+      </c>
+      <c r="D1179" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1179">
+        <v>0</v>
+      </c>
+      <c r="F1179" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1179" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1179" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1179" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1179" t="str">
+        <v>46.332804</v>
+      </c>
+      <c r="K1179" t="str">
+        <v>13.538685</v>
+      </c>
+      <c r="L1179" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1179" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1179" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1179" t="str">
+        <v>Didn't go.</v>
+      </c>
+      <c r="P1179" t="str">
+        <v/>
+      </c>
+      <c r="Q1179">
+        <v>3</v>
+      </c>
+      <c r="R1179" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers gluten-free pizza options. Family-run pizzeria with freshly baked pizzas. Highly praised for GF options and selection of beers.</v>
+      </c>
+      <c r="S1179" t="str">
+        <v/>
+      </c>
+      <c r="T1179" t="str">
+        <v/>
+      </c>
+      <c r="U1179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1180" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1180" t="str">
+        <v>Restavracija Letni vrt</v>
+      </c>
+      <c r="D1180" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1180">
+        <v>0</v>
+      </c>
+      <c r="F1180" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1180" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1180" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1180" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1180" t="str">
+        <v>46.337948</v>
+      </c>
+      <c r="K1180" t="str">
+        <v>13.55217</v>
+      </c>
+      <c r="L1180" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1180" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1180" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1180" t="str">
+        <v>Per FMGF staff is very knowledgable and it's more upscale so there are options such as risotto. Didn't go.</v>
+      </c>
+      <c r="P1180" t="str">
+        <v/>
+      </c>
+      <c r="Q1180">
+        <v>3</v>
+      </c>
+      <c r="R1180" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers vegetarian and GF options. Staff accommodating and helpful with GF requests. Have provided free GF bread with cheese to GF diners. Can customize dishes.</v>
+      </c>
+      <c r="S1180" t="str">
+        <v/>
+      </c>
+      <c r="T1180" t="str">
+        <v/>
+      </c>
+      <c r="U1180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1181" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1181" t="str">
+        <v>Brv Brjeka</v>
+      </c>
+      <c r="D1181" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1181">
+        <v>0</v>
+      </c>
+      <c r="F1181" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1181" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1181" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1181" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1181" t="str">
+        <v>46.332109</v>
+      </c>
+      <c r="K1181" t="str">
+        <v>13.58868</v>
+      </c>
+      <c r="L1181" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1181" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1181" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1181" t="str">
+        <v>Didn't go.</v>
+      </c>
+      <c r="P1181" t="str">
+        <v/>
+      </c>
+      <c r="Q1181" t="str">
+        <v/>
+      </c>
+      <c r="R1181" t="str">
+        <v/>
+      </c>
+      <c r="S1181" t="str">
+        <v/>
+      </c>
+      <c r="T1181" t="str">
+        <v/>
+      </c>
+      <c r="U1181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1182" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1182" t="str">
+        <v>Kobarid</v>
+      </c>
+      <c r="D1182" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1182">
+        <v>0</v>
+      </c>
+      <c r="F1182" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1182" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1182" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1182" t="str">
+        <v/>
+      </c>
+      <c r="J1182" t="str">
+        <v>46.247655</v>
+      </c>
+      <c r="K1182" t="str">
+        <v>13.579175</v>
+      </c>
+      <c r="L1182" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1182" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1182" t="str">
+        <v/>
+      </c>
+      <c r="O1182" t="str">
+        <v>Was debating between staying here or staying in Bovec. Glad I chose Bovec, but I did ride the bus through this town and it looked adorable. Maybe next time!</v>
+      </c>
+      <c r="P1182" t="str">
+        <v/>
+      </c>
+      <c r="Q1182" t="str">
+        <v/>
+      </c>
+      <c r="R1182" t="str">
+        <v/>
+      </c>
+      <c r="S1182" t="str">
+        <v/>
+      </c>
+      <c r="T1182" t="str">
+        <v/>
+      </c>
+      <c r="U1182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1183" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1183" t="str">
+        <v>Tolminska korita</v>
+      </c>
+      <c r="D1183" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1183">
+        <v>0</v>
+      </c>
+      <c r="F1183" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1183" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1183" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1183" t="str">
+        <v/>
+      </c>
+      <c r="J1183" t="str">
+        <v>46.198028</v>
+      </c>
+      <c r="K1183" t="str">
+        <v>13.740154</v>
+      </c>
+      <c r="L1183" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1183" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1183" t="str">
+        <v/>
+      </c>
+      <c r="O1183" t="str">
+        <v>Awesome looking cave/gorge thing with waterfalls. Didn't get a chance to visit.</v>
+      </c>
+      <c r="P1183" t="str">
+        <v/>
+      </c>
+      <c r="Q1183" t="str">
+        <v/>
+      </c>
+      <c r="R1183" t="str">
+        <v/>
+      </c>
+      <c r="S1183" t="str">
+        <v/>
+      </c>
+      <c r="T1183" t="str">
+        <v/>
+      </c>
+      <c r="U1183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1184" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1184" t="str">
+        <v>Soča Valley Nature Walks</v>
+      </c>
+      <c r="D1184" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1184">
+        <v>0</v>
+      </c>
+      <c r="F1184" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1184" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1184" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1184" t="str">
+        <v/>
+      </c>
+      <c r="J1184" t="str">
+        <v>46.24823</v>
+      </c>
+      <c r="K1184" t="str">
+        <v>13.577372</v>
+      </c>
+      <c r="L1184" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1184" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1184" t="str">
+        <v/>
+      </c>
+      <c r="O1184" t="str">
+        <v>Didn't get a chance to explore.</v>
+      </c>
+      <c r="P1184" t="str">
+        <v/>
+      </c>
+      <c r="Q1184" t="str">
+        <v/>
+      </c>
+      <c r="R1184" t="str">
+        <v/>
+      </c>
+      <c r="S1184" t="str">
+        <v/>
+      </c>
+      <c r="T1184" t="str">
+        <v/>
+      </c>
+      <c r="U1184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1185" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1185" t="str">
+        <v>Bohinjska Bistrica</v>
+      </c>
+      <c r="D1185" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1185" t="str">
+        <v/>
+      </c>
+      <c r="F1185" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1185" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1185" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1185" t="str">
+        <v/>
+      </c>
+      <c r="J1185" t="str">
+        <v>46.274273</v>
+      </c>
+      <c r="K1185" t="str">
+        <v>13.959222</v>
+      </c>
+      <c r="L1185" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1185" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1185" t="str">
+        <v/>
+      </c>
+      <c r="O1185" t="str">
+        <v/>
+      </c>
+      <c r="P1185" t="str">
+        <v/>
+      </c>
+      <c r="Q1185" t="str">
+        <v/>
+      </c>
+      <c r="R1185" t="str">
+        <v/>
+      </c>
+      <c r="S1185" t="str">
+        <v/>
+      </c>
+      <c r="T1185" t="str">
+        <v/>
+      </c>
+      <c r="U1185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1186" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1186" t="str">
+        <v>Sunrose 7 - Gourmet &amp; SPA Hotel Bohinj</v>
+      </c>
+      <c r="D1186" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1186">
+        <v>1</v>
+      </c>
+      <c r="F1186" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1186" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1186" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1186" t="str">
+        <v/>
+      </c>
+      <c r="J1186" t="str">
+        <v>46.271411</v>
+      </c>
+      <c r="K1186" t="str">
+        <v>13.95721</v>
+      </c>
+      <c r="L1186" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1186" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1186" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1186" t="str">
+        <v>Such an incredibly beautiful hotel tucked away in the 'city center' of Bohinj. They upgraded me to a room with a windowsill reading nook overlooking the garden and it was beautiful. I did not realize it was a digital detox (but they did have WiFi for the annoying people like me who just can't disconnect). The spa/wellness room is gorgeous - sauna, jacuzzi, cold shower, tea, water, sparkling wine, lounge beds. It was great. And I can't say enough good things about the dinner. They were able to accommodate GF pescatarian for their 4-course tasting menu and it was unbelievable. All for only 55 euros too! I added the wine pairing (4 glasses) for 20 euro additional. So beyond worth it. Wish I had been able to go back for a second night and enjoy again. The breakfast was also good - nice buffet spread with smoothies, juices, meats, cheeses, traditional dishes, make your own yogurt bowls, and then order a la carte eggs your way. Highly recommend both the hotel and the restaurant! The staff were unbelievably kind too!</v>
+      </c>
+      <c r="P1186" t="str">
+        <v/>
+      </c>
+      <c r="Q1186" t="str">
+        <v/>
+      </c>
+      <c r="R1186" t="str">
+        <v/>
+      </c>
+      <c r="S1186" t="str">
+        <v>https://www.hotels.com/ho2924730112/hotel-bohinj/</v>
+      </c>
+      <c r="T1186" t="str">
+        <v/>
+      </c>
+      <c r="U1186" t="str">
+        <v>Restaurant accommodated GF pescatarian for the full 4-course tasting menu. Breakfast buffet plus a la carte eggs.</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1187" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1187" t="str">
+        <v>Hotel Bohinj</v>
+      </c>
+      <c r="D1187" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1187">
+        <v>1</v>
+      </c>
+      <c r="F1187" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1187" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1187" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1187" t="str">
+        <v/>
+      </c>
+      <c r="J1187" t="str">
+        <v>46.277292</v>
+      </c>
+      <c r="K1187" t="str">
+        <v>13.888857</v>
+      </c>
+      <c r="L1187" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1187" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1187" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1187" t="str">
+        <v>Hotel was pricey but felt worth it. It's tucked back a little from the lake, but right next to the bus stop. I LOVED that they had a stationary bike and set of weights in the room since they do not have a gym. AC is environmentally friendly/sustainable, which is great, but means it does not get very cool. I was lucky I had a room with a balcony so I could leave the door open a bit at night to cool the room down. The wellness/spa was nice with a salt room, finnish sauna, turkish sauna, heated outdoor pool, etc. You need to book a time, but I like that it was included in the room price (at least for the room I got) because you had to pay extra to visit the sauna at a lot of the other hotels I stayed at in Slovenia. I had dinner at the hotel both nights I stayed - they had GF options marked and offered GF bread (though the bread was blehh). The trout carpaccio was delicious! Got it both nights. I'd pass on the risotto (it was kind of bland). I enjoyed the vegetable soup.</v>
+      </c>
+      <c r="P1187" t="str">
+        <v/>
+      </c>
+      <c r="Q1187" t="str">
+        <v/>
+      </c>
+      <c r="R1187" t="str">
+        <v/>
+      </c>
+      <c r="S1187" t="str">
+        <v/>
+      </c>
+      <c r="T1187" t="str">
+        <v/>
+      </c>
+      <c r="U1187" t="str">
+        <v>Dinner menu has GF options marked and GF bread available. Trout carpaccio recommended.</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1188" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1188" t="str">
+        <v>Lake Bohinj</v>
+      </c>
+      <c r="D1188" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1188">
+        <v>1</v>
+      </c>
+      <c r="F1188" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1188" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1188" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1188" t="str">
+        <v/>
+      </c>
+      <c r="J1188" t="str">
+        <v>46.28401</v>
+      </c>
+      <c r="K1188" t="str">
+        <v>13.859414</v>
+      </c>
+      <c r="L1188" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1188" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1188" t="str">
+        <v/>
+      </c>
+      <c r="O1188" t="str">
+        <v>Slovenia's largest lake. Beautiful to just wander around and walk around the lake. Much less touristy than Lake Bled.</v>
+      </c>
+      <c r="P1188" t="str">
+        <v/>
+      </c>
+      <c r="Q1188" t="str">
+        <v/>
+      </c>
+      <c r="R1188" t="str">
+        <v/>
+      </c>
+      <c r="S1188" t="str">
+        <v/>
+      </c>
+      <c r="T1188" t="str">
+        <v/>
+      </c>
+      <c r="U1188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1189" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1189" t="str">
+        <v>Mostnica Gorge</v>
+      </c>
+      <c r="D1189" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1189">
+        <v>0</v>
+      </c>
+      <c r="F1189" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1189" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1189" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1189" t="str">
+        <v/>
+      </c>
+      <c r="J1189" t="str">
+        <v>46.296092</v>
+      </c>
+      <c r="K1189" t="str">
+        <v>13.887576</v>
+      </c>
+      <c r="L1189" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1189" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1189" t="str">
+        <v/>
+      </c>
+      <c r="O1189" t="str">
+        <v>Didn't make it here!</v>
+      </c>
+      <c r="P1189" t="str">
+        <v/>
+      </c>
+      <c r="Q1189" t="str">
+        <v/>
+      </c>
+      <c r="R1189" t="str">
+        <v/>
+      </c>
+      <c r="S1189" t="str">
+        <v/>
+      </c>
+      <c r="T1189" t="str">
+        <v/>
+      </c>
+      <c r="U1189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1190" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1190" t="str">
+        <v>Seven Lakes Valley</v>
+      </c>
+      <c r="D1190" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1190">
+        <v>1</v>
+      </c>
+      <c r="F1190" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1190" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1190" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1190" t="str">
+        <v/>
+      </c>
+      <c r="J1190" t="str">
+        <v>46.317388</v>
+      </c>
+      <c r="K1190" t="str">
+        <v>13.780805</v>
+      </c>
+      <c r="L1190" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1190" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1190" t="str">
+        <v/>
+      </c>
+      <c r="O1190" t="str">
+        <v>This hike kind sucked ha. It was MUCH more difficult than I anticipated. Would highly recommend proper hiking boots and maybe even poles. The downhills can get pretty brutal at times. Make sure to download the trail map and know where you're going - I thought I downloaded the map, but it didn't actually work and I got very lost. Started the hike by taking a taxi (prebooked) at 6:30am from Hotel Bohinj up to Planina Blato, Trail starts uphill immediately to give you a taste for what you're in for. With losing the trail a couple times, not paying attention, and having to get all the way back down to the lake (Hotel Bohinj) unless I took public transport (did not have a taxi booked and did not have cell service most of the time) I ended up hiking ~30km and my legs and feet were HATING me. Ended up taking the path back down via Vogar but was too tired to go the 3 extra minutes to the viewpoint :D - just wanted to be done!</v>
+      </c>
+      <c r="P1190" t="str">
+        <v/>
+      </c>
+      <c r="Q1190" t="str">
+        <v/>
+      </c>
+      <c r="R1190" t="str">
+        <v/>
+      </c>
+      <c r="S1190" t="str">
+        <v/>
+      </c>
+      <c r="T1190" t="str">
+        <v/>
+      </c>
+      <c r="U1190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1191" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1191" t="str">
+        <v>Planina Blato - 7 Lakes Valley</v>
+      </c>
+      <c r="D1191" t="str">
+        <v>other</v>
+      </c>
+      <c r="E1191">
+        <v>1</v>
+      </c>
+      <c r="F1191" t="str">
+        <v>📍</v>
+      </c>
+      <c r="G1191" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1191" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1191" t="str">
+        <v/>
+      </c>
+      <c r="J1191" t="str">
+        <v>46.314571</v>
+      </c>
+      <c r="K1191" t="str">
+        <v>13.848824</v>
+      </c>
+      <c r="L1191" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1191" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1191" t="str">
+        <v/>
+      </c>
+      <c r="O1191" t="str">
+        <v>Easiest approach for the Seven Lakes Valley Hike. This is where I started. See my notes on the Seven Lakes Valley pin. Wasn't the biggest fan of this hike. Tried to descent via Slap Savica and got totally lost and ended up backtracking..</v>
+      </c>
+      <c r="P1191" t="str">
+        <v/>
+      </c>
+      <c r="Q1191" t="str">
+        <v/>
+      </c>
+      <c r="R1191" t="str">
+        <v/>
+      </c>
+      <c r="S1191" t="str">
+        <v/>
+      </c>
+      <c r="T1191" t="str">
+        <v/>
+      </c>
+      <c r="U1191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1192" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1192" t="str">
+        <v>Stara Fužina</v>
+      </c>
+      <c r="D1192" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1192">
+        <v>1</v>
+      </c>
+      <c r="F1192" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1192" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1192" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1192" t="str">
+        <v/>
+      </c>
+      <c r="J1192" t="str">
+        <v>46.288666</v>
+      </c>
+      <c r="K1192" t="str">
+        <v>13.894894</v>
+      </c>
+      <c r="L1192" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1192" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1192" t="str">
+        <v/>
+      </c>
+      <c r="O1192" t="str">
+        <v>Walked back through this town on the way back from the Seven Lakes Valley hike and it was so cute and picturesque.</v>
+      </c>
+      <c r="P1192" t="str">
+        <v/>
+      </c>
+      <c r="Q1192" t="str">
+        <v/>
+      </c>
+      <c r="R1192" t="str">
+        <v/>
+      </c>
+      <c r="S1192" t="str">
+        <v/>
+      </c>
+      <c r="T1192" t="str">
+        <v/>
+      </c>
+      <c r="U1192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1193" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1193" t="str">
+        <v>Savica Waterfall</v>
+      </c>
+      <c r="D1193" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1193" t="str">
+        <v/>
+      </c>
+      <c r="F1193" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1193" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1193" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1193" t="str">
+        <v/>
+      </c>
+      <c r="J1193" t="str">
+        <v>46.292737</v>
+      </c>
+      <c r="K1193" t="str">
+        <v>13.79677</v>
+      </c>
+      <c r="L1193" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1193" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1193" t="str">
+        <v/>
+      </c>
+      <c r="O1193" t="str">
+        <v/>
+      </c>
+      <c r="P1193" t="str">
+        <v/>
+      </c>
+      <c r="Q1193" t="str">
+        <v/>
+      </c>
+      <c r="R1193" t="str">
+        <v/>
+      </c>
+      <c r="S1193" t="str">
+        <v/>
+      </c>
+      <c r="T1193" t="str">
+        <v/>
+      </c>
+      <c r="U1193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1194" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1194" t="str">
+        <v>Vogar viewpoint - Lake Bohinj</v>
+      </c>
+      <c r="D1194" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1194">
+        <v>0</v>
+      </c>
+      <c r="F1194" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1194" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1194" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1194" t="str">
+        <v/>
+      </c>
+      <c r="J1194" t="str">
+        <v>46.295522</v>
+      </c>
+      <c r="K1194" t="str">
+        <v>13.864687</v>
+      </c>
+      <c r="L1194" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1194" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1194" t="str">
+        <v/>
+      </c>
+      <c r="O1194" t="str">
+        <v>Made it to the mountain hut (on the way back from Seven Lakes Valley hike) but didn't make it the 3 min more to the lookout point bc I was POOPED from my ~30k hike before :/ Trek down from Vogar seemed difficult (but maybe I took the wrong route).</v>
+      </c>
+      <c r="P1194" t="str">
+        <v/>
+      </c>
+      <c r="Q1194" t="str">
+        <v/>
+      </c>
+      <c r="R1194" t="str">
+        <v/>
+      </c>
+      <c r="S1194" t="str">
+        <v/>
+      </c>
+      <c r="T1194" t="str">
+        <v/>
+      </c>
+      <c r="U1194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1195" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1195" t="str">
+        <v>Vir, Bohinj</v>
+      </c>
+      <c r="D1195" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1195" t="str">
+        <v/>
+      </c>
+      <c r="F1195" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1195" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1195" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1195" t="str">
+        <v/>
+      </c>
+      <c r="J1195" t="str">
+        <v>46.281859</v>
+      </c>
+      <c r="K1195" t="str">
+        <v>13.880928</v>
+      </c>
+      <c r="L1195" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1195" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1195" t="str">
+        <v/>
+      </c>
+      <c r="O1195" t="str">
+        <v/>
+      </c>
+      <c r="P1195" t="str">
+        <v/>
+      </c>
+      <c r="Q1195" t="str">
+        <v/>
+      </c>
+      <c r="R1195" t="str">
+        <v/>
+      </c>
+      <c r="S1195" t="str">
+        <v/>
+      </c>
+      <c r="T1195" t="str">
+        <v/>
+      </c>
+      <c r="U1195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1196" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1196" t="str">
+        <v>Valley station - Vogel Cable Car</v>
+      </c>
+      <c r="D1196" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1196">
+        <v>0</v>
+      </c>
+      <c r="F1196" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1196" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1196" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1196" t="str">
+        <v/>
+      </c>
+      <c r="J1196" t="str">
+        <v>46.275721</v>
+      </c>
+      <c r="K1196" t="str">
+        <v>13.835417</v>
+      </c>
+      <c r="L1196" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1196" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1196" t="str">
+        <v/>
+      </c>
+      <c r="O1196" t="str">
+        <v>Cable car was closed for maintenance when I visited.</v>
+      </c>
+      <c r="P1196" t="str">
+        <v/>
+      </c>
+      <c r="Q1196" t="str">
+        <v/>
+      </c>
+      <c r="R1196" t="str">
+        <v/>
+      </c>
+      <c r="S1196" t="str">
+        <v/>
+      </c>
+      <c r="T1196" t="str">
+        <v/>
+      </c>
+      <c r="U1196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1197" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1197" t="str">
+        <v>Zlatorog Fairy Trail</v>
+      </c>
+      <c r="D1197" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1197">
+        <v>0</v>
+      </c>
+      <c r="F1197" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1197" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1197" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1197" t="str">
+        <v/>
+      </c>
+      <c r="J1197" t="str">
+        <v>46.27904</v>
+      </c>
+      <c r="K1197" t="str">
+        <v>13.8347</v>
+      </c>
+      <c r="L1197" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1197" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1197" t="str">
+        <v/>
+      </c>
+      <c r="O1197" t="str">
+        <v>Didn't get an opportunity to do this.</v>
+      </c>
+      <c r="P1197" t="str">
+        <v/>
+      </c>
+      <c r="Q1197" t="str">
+        <v/>
+      </c>
+      <c r="R1197" t="str">
+        <v/>
+      </c>
+      <c r="S1197" t="str">
+        <v/>
+      </c>
+      <c r="T1197" t="str">
+        <v/>
+      </c>
+      <c r="U1197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1198" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1198" t="str">
+        <v>Cerkev Sv. Janeza Krstnika</v>
+      </c>
+      <c r="D1198" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1198" t="str">
+        <v/>
+      </c>
+      <c r="F1198" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1198" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1198" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1198" t="str">
+        <v/>
+      </c>
+      <c r="J1198" t="str">
+        <v>46.278757</v>
+      </c>
+      <c r="K1198" t="str">
+        <v>13.887029</v>
+      </c>
+      <c r="L1198" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1198" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1198" t="str">
+        <v/>
+      </c>
+      <c r="O1198" t="str">
+        <v/>
+      </c>
+      <c r="P1198" t="str">
+        <v/>
+      </c>
+      <c r="Q1198" t="str">
+        <v/>
+      </c>
+      <c r="R1198" t="str">
+        <v/>
+      </c>
+      <c r="S1198" t="str">
+        <v/>
+      </c>
+      <c r="T1198" t="str">
+        <v/>
+      </c>
+      <c r="U1198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1199" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1199" t="str">
+        <v>Valley of the Seven Lakes Trailhead</v>
+      </c>
+      <c r="D1199" t="str">
+        <v>other</v>
+      </c>
+      <c r="E1199" t="str">
+        <v/>
+      </c>
+      <c r="F1199" t="str">
+        <v>📍</v>
+      </c>
+      <c r="G1199" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1199" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1199" t="str">
+        <v/>
+      </c>
+      <c r="J1199" t="str">
+        <v>46.31075</v>
+      </c>
+      <c r="K1199" t="str">
+        <v>13.849306</v>
+      </c>
+      <c r="L1199" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1199" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1199" t="str">
+        <v/>
+      </c>
+      <c r="O1199" t="str">
+        <v/>
+      </c>
+      <c r="P1199" t="str">
+        <v/>
+      </c>
+      <c r="Q1199" t="str">
+        <v/>
+      </c>
+      <c r="R1199" t="str">
+        <v/>
+      </c>
+      <c r="S1199" t="str">
+        <v/>
+      </c>
+      <c r="T1199" t="str">
+        <v/>
+      </c>
+      <c r="U1199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1200" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1200" t="str">
+        <v>Lake 1 - Jezero pod Vršacem</v>
+      </c>
+      <c r="D1200" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1200" t="str">
+        <v/>
+      </c>
+      <c r="F1200" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1200" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1200" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1200" t="str">
+        <v/>
+      </c>
+      <c r="J1200" t="str">
+        <v>46.359689</v>
+      </c>
+      <c r="K1200" t="str">
+        <v>13.79758</v>
+      </c>
+      <c r="L1200" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1200" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1200" t="str">
+        <v/>
+      </c>
+      <c r="O1200" t="str">
+        <v/>
+      </c>
+      <c r="P1200" t="str">
+        <v/>
+      </c>
+      <c r="Q1200" t="str">
+        <v/>
+      </c>
+      <c r="R1200" t="str">
+        <v/>
+      </c>
+      <c r="S1200" t="str">
+        <v/>
+      </c>
+      <c r="T1200" t="str">
+        <v/>
+      </c>
+      <c r="U1200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1201" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1201" t="str">
+        <v>Lake 3 - Brown Lake - Sedmero Triglavsko jezero-Rjavo jezero</v>
+      </c>
+      <c r="D1201" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1201" t="str">
+        <v/>
+      </c>
+      <c r="F1201" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1201" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1201" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1201" t="str">
+        <v/>
+      </c>
+      <c r="J1201" t="str">
+        <v>46.355427</v>
+      </c>
+      <c r="K1201" t="str">
+        <v>13.795587</v>
+      </c>
+      <c r="L1201" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1201" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1201" t="str">
+        <v/>
+      </c>
+      <c r="O1201" t="str">
+        <v/>
+      </c>
+      <c r="P1201" t="str">
+        <v/>
+      </c>
+      <c r="Q1201" t="str">
+        <v/>
+      </c>
+      <c r="R1201" t="str">
+        <v/>
+      </c>
+      <c r="S1201" t="str">
+        <v/>
+      </c>
+      <c r="T1201" t="str">
+        <v/>
+      </c>
+      <c r="U1201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1202" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1202" t="str">
+        <v>Lake 4 - Green Lake - Sedmero Triglavsko jezero-Zeleno jezero</v>
+      </c>
+      <c r="D1202" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1202" t="str">
+        <v/>
+      </c>
+      <c r="F1202" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1202" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1202" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1202" t="str">
+        <v/>
+      </c>
+      <c r="J1202" t="str">
+        <v>46.351253</v>
+      </c>
+      <c r="K1202" t="str">
+        <v>13.794758</v>
+      </c>
+      <c r="L1202" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1202" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1202" t="str">
+        <v/>
+      </c>
+      <c r="O1202" t="str">
+        <v/>
+      </c>
+      <c r="P1202" t="str">
+        <v/>
+      </c>
+      <c r="Q1202" t="str">
+        <v/>
+      </c>
+      <c r="R1202" t="str">
+        <v/>
+      </c>
+      <c r="S1202" t="str">
+        <v/>
+      </c>
+      <c r="T1202" t="str">
+        <v/>
+      </c>
+      <c r="U1202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1203" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1203" t="str">
+        <v>Lake 5 - The Great (Kidney) Lake - Sedmero Triglavsko jezero - Jezero v Ledvicah</v>
+      </c>
+      <c r="D1203" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1203" t="str">
+        <v/>
+      </c>
+      <c r="F1203" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1203" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1203" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1203" t="str">
+        <v/>
+      </c>
+      <c r="J1203" t="str">
+        <v>46.340593</v>
+      </c>
+      <c r="K1203" t="str">
+        <v>13.782688</v>
+      </c>
+      <c r="L1203" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1203" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1203" t="str">
+        <v/>
+      </c>
+      <c r="O1203" t="str">
+        <v/>
+      </c>
+      <c r="P1203" t="str">
+        <v/>
+      </c>
+      <c r="Q1203" t="str">
+        <v/>
+      </c>
+      <c r="R1203" t="str">
+        <v/>
+      </c>
+      <c r="S1203" t="str">
+        <v/>
+      </c>
+      <c r="T1203" t="str">
+        <v/>
+      </c>
+      <c r="U1203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1204" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1204" t="str">
+        <v>Lake 6 - The Double Lake - Sedmero Triglavsko jezero-Dvojno jezero</v>
+      </c>
+      <c r="D1204" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1204">
+        <v>1</v>
+      </c>
+      <c r="F1204" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1204" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1204" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1204" t="str">
+        <v/>
+      </c>
+      <c r="J1204" t="str">
+        <v>46.316614</v>
+      </c>
+      <c r="K1204" t="str">
+        <v>13.779066</v>
+      </c>
+      <c r="L1204" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1204" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1204" t="str">
+        <v/>
+      </c>
+      <c r="O1204" t="str">
+        <v>Made it here on the 7 lakes valley hike! hah</v>
+      </c>
+      <c r="P1204" t="str">
+        <v/>
+      </c>
+      <c r="Q1204" t="str">
+        <v/>
+      </c>
+      <c r="R1204" t="str">
+        <v/>
+      </c>
+      <c r="S1204" t="str">
+        <v/>
+      </c>
+      <c r="T1204" t="str">
+        <v/>
+      </c>
+      <c r="U1204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1205" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1205" t="str">
+        <v>Lake 7 - The Black Lake</v>
+      </c>
+      <c r="D1205" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1205" t="str">
+        <v/>
+      </c>
+      <c r="F1205" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1205" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1205" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1205" t="str">
+        <v/>
+      </c>
+      <c r="J1205" t="str">
+        <v>46.298641</v>
+      </c>
+      <c r="K1205" t="str">
+        <v>13.795618</v>
+      </c>
+      <c r="L1205" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1205" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1205" t="str">
+        <v/>
+      </c>
+      <c r="O1205" t="str">
+        <v/>
+      </c>
+      <c r="P1205" t="str">
+        <v/>
+      </c>
+      <c r="Q1205" t="str">
+        <v/>
+      </c>
+      <c r="R1205" t="str">
+        <v/>
+      </c>
+      <c r="S1205" t="str">
+        <v/>
+      </c>
+      <c r="T1205" t="str">
+        <v/>
+      </c>
+      <c r="U1205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1206" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1206" t="str">
+        <v>Triglav National Park</v>
+      </c>
+      <c r="D1206" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1206">
+        <v>1</v>
+      </c>
+      <c r="F1206" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1206" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1206" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1206" t="str">
+        <v/>
+      </c>
+      <c r="J1206" t="str">
+        <v>46.342473</v>
+      </c>
+      <c r="K1206" t="str">
+        <v>13.799043</v>
+      </c>
+      <c r="L1206" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1206" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1206" t="str">
+        <v/>
+      </c>
+      <c r="O1206" t="str">
+        <v/>
+      </c>
+      <c r="P1206" t="str">
+        <v/>
+      </c>
+      <c r="Q1206" t="str">
+        <v/>
+      </c>
+      <c r="R1206" t="str">
+        <v/>
+      </c>
+      <c r="S1206" t="str">
+        <v/>
+      </c>
+      <c r="T1206" t="str">
+        <v/>
+      </c>
+      <c r="U1206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1207" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1207" t="str">
+        <v>Restavracija Kramar</v>
+      </c>
+      <c r="D1207" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1207">
+        <v>1</v>
+      </c>
+      <c r="F1207" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1207" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1207" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1207" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1207" t="str">
+        <v>46.281466</v>
+      </c>
+      <c r="K1207" t="str">
+        <v>13.881315</v>
+      </c>
+      <c r="L1207" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1207" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1207" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1207" t="str">
+        <v>Stopped here for lunch one day to have a caprese salad. Was great and the view can't be beat. Gets super crowded (even if offseason) though I was there on a Friday or Saturday so maybe that's to be expected.</v>
+      </c>
+      <c r="P1207" t="str">
+        <v/>
+      </c>
+      <c r="Q1207">
+        <v>3</v>
+      </c>
+      <c r="R1207" t="str">
+        <v>[2026-10-09 research] Lakeside restaurant with diverse menu including pizzas, burgers, vegetarian options. Pizza dough does not contain milk. Specific GF options not verified; recommend contacting directly.</v>
+      </c>
+      <c r="S1207" t="str">
+        <v/>
+      </c>
+      <c r="T1207" t="str">
+        <v/>
+      </c>
+      <c r="U1207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1208" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1208" t="str">
+        <v>Restaurant Mihovc</v>
+      </c>
+      <c r="D1208" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1208">
+        <v>0</v>
+      </c>
+      <c r="F1208" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1208" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1208" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1208" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1208" t="str">
+        <v>46.288691</v>
+      </c>
+      <c r="K1208" t="str">
+        <v>13.894666</v>
+      </c>
+      <c r="L1208" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1208" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1208" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1208" t="str">
+        <v>Didn't make it here. But according to reviews, they seem knowledgeable about gluten but cannot guarantee no CC. Like most places, they have allergens marked on the menu.</v>
+      </c>
+      <c r="P1208" t="str">
+        <v/>
+      </c>
+      <c r="Q1208">
+        <v>3</v>
+      </c>
+      <c r="R1208" t="str">
+        <v>[2026-10-09 research] Oldest restaurant in Bohinj (established 1888). Offers gluten-free options along with vegetarian and vegan. Fresh mountain setting. Staff accommodating to GF requests. Allergens marked on menu.</v>
+      </c>
+      <c r="S1208" t="str">
+        <v/>
+      </c>
+      <c r="T1208" t="str">
+        <v/>
+      </c>
+      <c r="U1208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1209" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1209" t="str">
+        <v>Hotel Gasperin Bohinj</v>
+      </c>
+      <c r="D1209" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1209">
+        <v>0</v>
+      </c>
+      <c r="F1209" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1209" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1209" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1209" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1209" t="str">
+        <v>46.274965</v>
+      </c>
+      <c r="K1209" t="str">
+        <v>13.891465</v>
+      </c>
+      <c r="L1209" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1209" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1209" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1209" t="str">
+        <v>Didn't visit - reviews say excellent breakfast with GF options (but seems only for hotel guests)</v>
+      </c>
+      <c r="P1209" t="str">
+        <v>https://www.findmeglutenfree.com/biz/hotel-gasperin-bohinj/5924316093480960</v>
+      </c>
+      <c r="Q1209">
+        <v>4</v>
+      </c>
+      <c r="R1209" t="str">
+        <v>[2026-10-09 research] Extensive gluten-free and dairy-free breakfast. Home-baked GF and non-GF options. GF items in dedicated cases. Owner follows GF diet and is knowledgeable. Pack lunch available for fee.</v>
+      </c>
+      <c r="S1209" t="str">
+        <v/>
+      </c>
+      <c r="T1209" t="str">
+        <v/>
+      </c>
+      <c r="U1209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1210" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1210" t="str">
+        <v>Hiša Pr' Pristavc - gostilna in pizzerija</v>
+      </c>
+      <c r="D1210" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1210">
+        <v>0</v>
+      </c>
+      <c r="F1210" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1210" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1210" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1210" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1210" t="str">
+        <v>46.267939</v>
+      </c>
+      <c r="K1210" t="str">
+        <v>13.909704</v>
+      </c>
+      <c r="L1210" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1210" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1210" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1210" t="str">
+        <v>Didn't visit - but it looks like they are able to make fish (trout) and potato dishes GF and have allergens marked on the menu (like most places in Slovenia)</v>
+      </c>
+      <c r="P1210" t="str">
+        <v/>
+      </c>
+      <c r="Q1210">
+        <v>3</v>
+      </c>
+      <c r="R1210" t="str">
+        <v>[2026-10-09 research] Gostilna and pizzeria in 19th century building. Offers gluten-free menu with items like beef ribs, seafood, steak, calamari. Staff helpful in modifying items. Over 26 wood-fired pizzas.</v>
+      </c>
+      <c r="S1210" t="str">
+        <v/>
+      </c>
+      <c r="T1210" t="str">
+        <v/>
+      </c>
+      <c r="U1210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1211" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1211" t="str">
+        <v>Bled Rose Hotel</v>
+      </c>
+      <c r="D1211" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1211">
+        <v>1</v>
+      </c>
+      <c r="F1211" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1211" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1211" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1211" t="str">
+        <v/>
+      </c>
+      <c r="J1211" t="str">
+        <v>46.371006</v>
+      </c>
+      <c r="K1211" t="str">
+        <v>14.106239</v>
+      </c>
+      <c r="L1211" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1211" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1211" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1211" t="str">
+        <v>Seems to be one of the nicer hotels in Bled. Slightly offset from the lake, but steps from one of the main bus stations and close to the castle, gorge, main tourist shops and restaurants, etc. There was a conference/corporate thing going on when I visited which was a little frustrating just because they did not have things open as expected - they weren't serving lunch the day I got in, the bar was closed early at night, etc. I also tried to make a reservation at their bistro for dinner one night but got no response. When I walked by it seemed pretty empty so not sure what gives. The front desk staff was hit or miss - some were friendly, some were terribly unhelpful. I booked the wellness room (upcharge) and it was okay, though the jacuzzi was not working and one of the saunas was off as well. Not sure it was worth it...I did not have a hanging 'do not disturb' sign, though I saw other rooms had them. I did use the digital 'do not disturb' button but it didn't seem to do anything since housekeeping came in regardless. I think if I find myself in Bled again I'd probably try a different hotel.</v>
+      </c>
+      <c r="P1211" t="str">
+        <v/>
+      </c>
+      <c r="Q1211" t="str">
+        <v/>
+      </c>
+      <c r="R1211" t="str">
+        <v/>
+      </c>
+      <c r="S1211" t="str">
+        <v>https://www.hotels.com/ho293139/bled-rose-hotel-bled-slovenia/</v>
+      </c>
+      <c r="T1211" t="str">
+        <v/>
+      </c>
+      <c r="U1211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1212" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1212" t="str">
+        <v>Church of the Assumption of the Blessed Virgin Mary</v>
+      </c>
+      <c r="D1212" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1212">
+        <v>1</v>
+      </c>
+      <c r="F1212" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1212" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1212" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1212" t="str">
+        <v/>
+      </c>
+      <c r="J1212" t="str">
+        <v>46.362576</v>
+      </c>
+      <c r="K1212" t="str">
+        <v>14.090218</v>
+      </c>
+      <c r="L1212" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1212" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1212" t="str">
+        <v/>
+      </c>
+      <c r="O1212" t="str">
+        <v>Visit the church on the island and ring the wishing bell! I think it cost 12 or 15 euro to get in and they take credit cards.</v>
+      </c>
+      <c r="P1212" t="str">
+        <v/>
+      </c>
+      <c r="Q1212" t="str">
+        <v/>
+      </c>
+      <c r="R1212" t="str">
+        <v/>
+      </c>
+      <c r="S1212" t="str">
+        <v/>
+      </c>
+      <c r="T1212" t="str">
+        <v/>
+      </c>
+      <c r="U1212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1213" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1213" t="str">
+        <v>Ojstrica Viewpoint</v>
+      </c>
+      <c r="D1213" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1213">
+        <v>1</v>
+      </c>
+      <c r="F1213" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1213" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1213" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1213" t="str">
+        <v/>
+      </c>
+      <c r="J1213" t="str">
+        <v>46.359556</v>
+      </c>
+      <c r="K1213" t="str">
+        <v>14.078576</v>
+      </c>
+      <c r="L1213" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1213" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1213" t="str">
+        <v/>
+      </c>
+      <c r="O1213" t="str">
+        <v>Gorgeous viewpoint. Must go! Very quick but pretty steep hike. There are cables to hold on to towards the top.</v>
+      </c>
+      <c r="P1213" t="str">
+        <v/>
+      </c>
+      <c r="Q1213" t="str">
+        <v/>
+      </c>
+      <c r="R1213" t="str">
+        <v/>
+      </c>
+      <c r="S1213" t="str">
+        <v/>
+      </c>
+      <c r="T1213" t="str">
+        <v/>
+      </c>
+      <c r="U1213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1214" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1214" t="str">
+        <v>Mala Osojnica</v>
+      </c>
+      <c r="D1214" t="str">
+        <v>viewpoint</v>
+      </c>
+      <c r="E1214">
+        <v>1</v>
+      </c>
+      <c r="F1214" t="str">
+        <v>🌅</v>
+      </c>
+      <c r="G1214" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1214" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1214" t="str">
+        <v/>
+      </c>
+      <c r="J1214" t="str">
+        <v>46.356929</v>
+      </c>
+      <c r="K1214" t="str">
+        <v>14.082363</v>
+      </c>
+      <c r="L1214" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1214" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1214" t="str">
+        <v/>
+      </c>
+      <c r="O1214" t="str">
+        <v/>
+      </c>
+      <c r="P1214" t="str">
+        <v/>
+      </c>
+      <c r="Q1214" t="str">
+        <v/>
+      </c>
+      <c r="R1214" t="str">
+        <v/>
+      </c>
+      <c r="S1214" t="str">
+        <v/>
+      </c>
+      <c r="T1214" t="str">
+        <v/>
+      </c>
+      <c r="U1214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1215" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1215" t="str">
+        <v>Mala Osojnica Trailhead</v>
+      </c>
+      <c r="D1215" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1215">
+        <v>1</v>
+      </c>
+      <c r="F1215" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1215" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1215" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1215" t="str">
+        <v/>
+      </c>
+      <c r="J1215" t="str">
+        <v>46.358806</v>
+      </c>
+      <c r="K1215" t="str">
+        <v>14.085417</v>
+      </c>
+      <c r="L1215" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1215" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1215" t="str">
+        <v/>
+      </c>
+      <c r="O1215" t="str">
+        <v>Ojstrica was definitely the better viewpoint, but this hike is worth doing too since you're already there. It's not much further, and WAY less people venture up to it, so you have a chance to be up there alone if you hang out for a few minutes.</v>
+      </c>
+      <c r="P1215" t="str">
+        <v/>
+      </c>
+      <c r="Q1215" t="str">
+        <v/>
+      </c>
+      <c r="R1215" t="str">
+        <v/>
+      </c>
+      <c r="S1215" t="str">
+        <v/>
+      </c>
+      <c r="T1215" t="str">
+        <v/>
+      </c>
+      <c r="U1215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1216" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1216" t="str">
+        <v>Lake Bled</v>
+      </c>
+      <c r="D1216" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1216">
+        <v>1</v>
+      </c>
+      <c r="F1216" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1216" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1216" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1216" t="str">
+        <v/>
+      </c>
+      <c r="J1216" t="str">
+        <v>46.363598</v>
+      </c>
+      <c r="K1216" t="str">
+        <v>14.093805</v>
+      </c>
+      <c r="L1216" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1216" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1216" t="str">
+        <v/>
+      </c>
+      <c r="O1216" t="str">
+        <v>Gorgeous lake! Definitely walk around the entire thing - the sides are very different from each other, but there are beautiful views the whole way.</v>
+      </c>
+      <c r="P1216" t="str">
+        <v/>
+      </c>
+      <c r="Q1216" t="str">
+        <v/>
+      </c>
+      <c r="R1216" t="str">
+        <v/>
+      </c>
+      <c r="S1216" t="str">
+        <v/>
+      </c>
+      <c r="T1216" t="str">
+        <v/>
+      </c>
+      <c r="U1216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1217" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1217" t="str">
+        <v>Vintgar Gorge Parking</v>
+      </c>
+      <c r="D1217" t="str">
+        <v>other</v>
+      </c>
+      <c r="E1217" t="str">
+        <v/>
+      </c>
+      <c r="F1217" t="str">
+        <v>📍</v>
+      </c>
+      <c r="G1217" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1217" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1217" t="str">
+        <v/>
+      </c>
+      <c r="J1217" t="str">
+        <v>46.379138</v>
+      </c>
+      <c r="K1217" t="str">
+        <v>14.086324</v>
+      </c>
+      <c r="L1217" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1217" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1217" t="str">
+        <v/>
+      </c>
+      <c r="O1217" t="str">
+        <v/>
+      </c>
+      <c r="P1217" t="str">
+        <v/>
+      </c>
+      <c r="Q1217" t="str">
+        <v/>
+      </c>
+      <c r="R1217" t="str">
+        <v/>
+      </c>
+      <c r="S1217" t="str">
+        <v/>
+      </c>
+      <c r="T1217" t="str">
+        <v/>
+      </c>
+      <c r="U1217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1218" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1218" t="str">
+        <v>Zipline Dolinka Bled – Zipline Experience at Lake Bled</v>
+      </c>
+      <c r="D1218" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1218">
+        <v>0</v>
+      </c>
+      <c r="F1218" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1218" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1218" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1218" t="str">
+        <v/>
+      </c>
+      <c r="J1218" t="str">
+        <v>46.370921</v>
+      </c>
+      <c r="K1218" t="str">
+        <v>14.107826</v>
+      </c>
+      <c r="L1218" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1218" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1218" t="str">
+        <v/>
+      </c>
+      <c r="O1218" t="str">
+        <v>Didn't do this since I had just done the zipline in Bovec.</v>
+      </c>
+      <c r="P1218" t="str">
+        <v/>
+      </c>
+      <c r="Q1218" t="str">
+        <v/>
+      </c>
+      <c r="R1218" t="str">
+        <v/>
+      </c>
+      <c r="S1218" t="str">
+        <v/>
+      </c>
+      <c r="T1218" t="str">
+        <v/>
+      </c>
+      <c r="U1218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1219" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1219" t="str">
+        <v>Bled Castle</v>
+      </c>
+      <c r="D1219" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1219">
+        <v>1</v>
+      </c>
+      <c r="F1219" t="str">
+        <v>🏰</v>
+      </c>
+      <c r="G1219" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1219" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1219" t="str">
+        <v/>
+      </c>
+      <c r="J1219" t="str">
+        <v>46.369915</v>
+      </c>
+      <c r="K1219" t="str">
+        <v>14.100622</v>
+      </c>
+      <c r="L1219" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1219" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1219" t="str">
+        <v/>
+      </c>
+      <c r="O1219" t="str">
+        <v>Beautiful castle. You can walk up to a viewpoint just below the castle for free. If you want to explore the castle grounds and additional viewpoints, you need to pay to get in. I went around 6pm and it wasn't too crowded (they close at 8pm - at least when I was there). You can go to the castle wine cellar and taste various wines for 2.50 euro.</v>
+      </c>
+      <c r="P1219" t="str">
+        <v/>
+      </c>
+      <c r="Q1219" t="str">
+        <v/>
+      </c>
+      <c r="R1219" t="str">
+        <v/>
+      </c>
+      <c r="S1219" t="str">
+        <v/>
+      </c>
+      <c r="T1219" t="str">
+        <v/>
+      </c>
+      <c r="U1219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1220" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1220" t="str">
+        <v>Art Cafe Bar</v>
+      </c>
+      <c r="D1220" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1220">
+        <v>1</v>
+      </c>
+      <c r="F1220" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1220" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1220" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1220" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1220" t="str">
+        <v>46.370278</v>
+      </c>
+      <c r="K1220" t="str">
+        <v>14.106944</v>
+      </c>
+      <c r="L1220" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1220" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1220" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1220" t="str">
+        <v>Went here late one night after being turned away from ARROI (because they could not guarantee GF). I got the shrimp risotto, which was marked GF on the menu. It wasn't the best thing I've ever had but if was good and I didn't get sick.</v>
+      </c>
+      <c r="P1220" t="str">
+        <v>https://www.findmeglutenfree.com/biz/art-cafe-bar/4738761999646720</v>
+      </c>
+      <c r="Q1220">
+        <v>3</v>
+      </c>
+      <c r="R1220" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers gluten-free menu with risotto (15+ reports), seafood risotto, prawn risotto marked GF. Has dedicated GF fryer but contains gluten in kitchen.</v>
+      </c>
+      <c r="S1220" t="str">
+        <v/>
+      </c>
+      <c r="T1220" t="str">
+        <v/>
+      </c>
+      <c r="U1220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1221" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1221" t="str">
+        <v>Public &amp; Vegan Kitchen Bled</v>
+      </c>
+      <c r="D1221" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1221">
+        <v>0</v>
+      </c>
+      <c r="F1221" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1221" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1221" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1221" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1221" t="str">
+        <v>46.366698</v>
+      </c>
+      <c r="K1221" t="str">
+        <v>14.109604</v>
+      </c>
+      <c r="L1221" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1221" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1221" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1221" t="str">
+        <v>Did not end up eating here.</v>
+      </c>
+      <c r="P1221" t="str">
+        <v>https://www.findmeglutenfree.com/biz/public-and-vegan-kitchen/5989320236859392</v>
+      </c>
+      <c r="Q1221">
+        <v>4</v>
+      </c>
+      <c r="R1221" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers gluten-free bread/buns, cakes, veggie burgers, fritters, GF beer. Ranked #1 restaurant in Bled. Staff knowledgeable about coeliac disease.</v>
+      </c>
+      <c r="S1221" t="str">
+        <v/>
+      </c>
+      <c r="T1221" t="str">
+        <v/>
+      </c>
+      <c r="U1221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1222" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1222" t="str">
+        <v>ARROI Restaurant</v>
+      </c>
+      <c r="D1222" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1222">
+        <v>1</v>
+      </c>
+      <c r="F1222" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1222" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1222" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1222" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1222" t="str">
+        <v>46.367227</v>
+      </c>
+      <c r="K1222" t="str">
+        <v>14.108879</v>
+      </c>
+      <c r="L1222" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1222" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1222" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1222" t="str">
+        <v>Was excited to try this place based on other reviews. The waiter was very nice but said he would not recommend the eating anything there if I had a gluten allergy. He said they don’t have a separate kitchen so they can’t certify that it doesn’t have traces of gluten. I asked about sushi and asked if they could just make it in a clean area and he said they could not. Since I have Celiac, I wasn’t going to chance it and left. He said the only safe place for Celiacs is a 30-minute drive outside of town. (Want to just say that the 100% prefer being turned away over getting sick so I definitely appreciate the waiter! Just feel like something must’ve happened in Lake Bled because places seem really overly cautious. I know as a Celiac any time I am dining out - even at dedicated GF restaurants - I’m taking a risk. I’m typically fine to take that risk as long as I know they will do their best to keep it safe)</v>
+      </c>
+      <c r="P1222" t="str">
+        <v>https://www.findmeglutenfree.com/biz/arroi-restaurant/6062215347699712</v>
+      </c>
+      <c r="Q1222">
+        <v>1</v>
+      </c>
+      <c r="R1222" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Offers GF pad thai, tofu, sushi, curry. Staff knowledgeable about coeliac. Complimentary GF appetizer for celiac guests. No guaranteed CC prevention.</v>
+      </c>
+      <c r="S1222" t="str">
+        <v/>
+      </c>
+      <c r="T1222" t="str">
+        <v/>
+      </c>
+      <c r="U1222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1223" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1223" t="str">
+        <v>Spica - Bar And Restaurant</v>
+      </c>
+      <c r="D1223" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1223">
+        <v>1</v>
+      </c>
+      <c r="F1223" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1223" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1223" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1223" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1223" t="str">
+        <v>46.369912</v>
+      </c>
+      <c r="K1223" t="str">
+        <v>14.107261</v>
+      </c>
+      <c r="L1223" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1223" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1223" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1223" t="str">
+        <v>Went for dinner twice in two days. Great location and beautiful outdoor area - was busy both times. I had the trout poke bowl the first time and it was delicious - the sauce is not GF but luckily I carry my own GF tamari packets so problem solved :) I especially enjoyed the seaweed salad in the poke bowl. I should've had the trout poke bowl again the second night, but the pizzas looked really great and I saw other reviews about how much care they take with GF pizzas cooking them on their own foil, etc. The pizza was really good and was cooked on its own foil, but I did not feel too great afterwards. It could've been for other reasons, but I would just take care if ordering pizza. But definitely go to Spica if you're in Bled! The staff are really nice too.</v>
+      </c>
+      <c r="P1223" t="str">
+        <v>https://www.findmeglutenfree.com/biz/spica/4918283660296192</v>
+      </c>
+      <c r="Q1223">
+        <v>3</v>
+      </c>
+      <c r="R1223" t="str">
+        <v>[2026-10-09 research] Not dedicated GF. Gluten-free pizza cooked on foil tin. All pizzas available as GF. Offers trout poke bowl marked GF. Lake view setting. Staff accommodating.</v>
+      </c>
+      <c r="S1223" t="str">
+        <v/>
+      </c>
+      <c r="T1223" t="str">
+        <v/>
+      </c>
+      <c r="U1223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1224" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="C1224" t="str">
+        <v>Lincer proizvodnja, trgovina in storitve Kranj, d.o.o.</v>
+      </c>
+      <c r="D1224" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1224">
+        <v>1</v>
+      </c>
+      <c r="F1224" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1224" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1224" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1224" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1224" t="str">
+        <v>46.361295</v>
+      </c>
+      <c r="K1224" t="str">
+        <v>14.15901</v>
+      </c>
+      <c r="L1224" t="str">
+        <v>Slovenia (October 2026)</v>
+      </c>
+      <c r="M1224" t="str">
+        <v>Bled</v>
+      </c>
+      <c r="N1224" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1224" t="str">
+        <v>Dedicated GF - you must go! It's a short bus ride from Bled and the buses run pretty consistently, even in the 'offseason.' I had a margarita pizza and peach iced tea for lunch, and then took a slice of blueberry cake, a figaro bar, and a chocolate bar to go. The pizza was delicious and I was so relieved to be eating something I knew was going to be safe after having a few gluten issues on the trip otherwise. Wish I had gotten more pieces of cake to take back and try!</v>
+      </c>
+      <c r="P1224" t="str">
+        <v>https://www.findmeglutenfree.com/biz/lincer/5560403728924672</v>
+      </c>
+      <c r="Q1224">
+        <v>5</v>
+      </c>
+      <c r="R1224" t="str">
+        <v>[2026-10-09 research] 100% dedicated gluten-free bakery, cafe and pizzeria. Offers GF cakes, desserts, pizza, cookies. Entire range is gluten-free. Friendly, knowledgeable staff. Delivery available throughout Slovenia.</v>
+      </c>
+      <c r="S1224" t="str">
+        <v/>
+      </c>
+      <c r="T1224" t="str">
+        <v/>
+      </c>
+      <c r="U1224" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1224"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1224"/>
+  <dimension ref="A1:U1225"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -74386,8 +74386,8 @@
       <c r="D1139" t="str">
         <v>bakery</v>
       </c>
-      <c r="E1139" t="str">
-        <v/>
+      <c r="E1139">
+        <v>1</v>
       </c>
       <c r="F1139" t="str">
         <v>🥐</v>
@@ -74426,7 +74426,7 @@
         <v>5</v>
       </c>
       <c r="R1139" t="str">
-        <v>[2026-10-09 research] 100% gluten-free dedicated bakery with large selection of GF baked goods. Offers cinnamon rolls, pastries, bread, cookies, mini pizza, bread with sausage. Everything preorder.</v>
+        <v>[2026-10-09 research] 100% gluten-free dedicated bakery with large selection of GF baked goods. Offers cinnamon rolls, pastries, bread, cookies, mini pizza, bread with sausage. Everything preorder. | Kelly 2026-10-10: selection not that big. Had a hazelnut chocolate cake slice (really good) and 2 cake pops (REALLY good).</v>
       </c>
       <c r="S1139" t="str">
         <v/>
@@ -79963,9 +79963,74 @@
         <v/>
       </c>
     </row>
+    <row r="1225">
+      <c r="A1225" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1225" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="C1225" t="str">
+        <v>Neks Lounge Bar (letter to your future self)</v>
+      </c>
+      <c r="D1225" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1225">
+        <v>1</v>
+      </c>
+      <c r="F1225" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1225" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1225" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1225" t="str">
+        <v/>
+      </c>
+      <c r="J1225" t="str">
+        <v>46.0473</v>
+      </c>
+      <c r="K1225" t="str">
+        <v>14.5014</v>
+      </c>
+      <c r="L1225" t="str">
+        <v>Kelly (added 2026-10-10, not on map)</v>
+      </c>
+      <c r="M1225" t="str">
+        <v>Ljubljana</v>
+      </c>
+      <c r="N1225" t="str">
+        <v/>
+      </c>
+      <c r="O1225" t="str">
+        <v>One of the best things I did in Ljubljana — wrote a letter to my future self, sealed with wax; Neks mails it 2 years later. Had a matcha latte.</v>
+      </c>
+      <c r="P1225" t="str">
+        <v/>
+      </c>
+      <c r="Q1225" t="str">
+        <v/>
+      </c>
+      <c r="R1225" t="str">
+        <v/>
+      </c>
+      <c r="S1225" t="str">
+        <v>https://neksljubljana.si/en</v>
+      </c>
+      <c r="T1225" t="str">
+        <v/>
+      </c>
+      <c r="U1225" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1225"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1225"/>
+  <dimension ref="A1:U1226"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -80028,9 +80028,74 @@
         <v/>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1226" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="C1226" t="str">
+        <v>Aktivni Planet (Soča rafting)</v>
+      </c>
+      <c r="D1226" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1226">
+        <v>1</v>
+      </c>
+      <c r="F1226" t="str">
+        <v>🎯</v>
+      </c>
+      <c r="G1226" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1226" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1226" t="str">
+        <v/>
+      </c>
+      <c r="J1226" t="str">
+        <v/>
+      </c>
+      <c r="K1226" t="str">
+        <v/>
+      </c>
+      <c r="L1226" t="str">
+        <v>Kelly (added 2026-10-10, not on map)</v>
+      </c>
+      <c r="M1226" t="str">
+        <v>Soča Valley</v>
+      </c>
+      <c r="N1226" t="str">
+        <v/>
+      </c>
+      <c r="O1226" t="str">
+        <v>Went rafting on the Soča with Aktivni Planet in Bovec. Guide was an 8x world champion rafter from Brazil.</v>
+      </c>
+      <c r="P1226" t="str">
+        <v/>
+      </c>
+      <c r="Q1226" t="str">
+        <v/>
+      </c>
+      <c r="R1226" t="str">
+        <v/>
+      </c>
+      <c r="S1226" t="str">
+        <v>https://aktivniplanet.si/en/</v>
+      </c>
+      <c r="T1226" t="str">
+        <v/>
+      </c>
+      <c r="U1226" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1225"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1226"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1226"/>
+  <dimension ref="A1:U1227"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -77475,7 +77475,7 @@
         <v>Such an incredibly beautiful hotel tucked away in the 'city center' of Bohinj. They upgraded me to a room with a windowsill reading nook overlooking the garden and it was beautiful. I did not realize it was a digital detox (but they did have WiFi for the annoying people like me who just can't disconnect). The spa/wellness room is gorgeous - sauna, jacuzzi, cold shower, tea, water, sparkling wine, lounge beds. It was great. And I can't say enough good things about the dinner. They were able to accommodate GF pescatarian for their 4-course tasting menu and it was unbelievable. All for only 55 euros too! I added the wine pairing (4 glasses) for 20 euro additional. So beyond worth it. Wish I had been able to go back for a second night and enjoy again. The breakfast was also good - nice buffet spread with smoothies, juices, meats, cheeses, traditional dishes, make your own yogurt bowls, and then order a la carte eggs your way. Highly recommend both the hotel and the restaurant! The staff were unbelievably kind too!</v>
       </c>
       <c r="P1186" t="str">
-        <v/>
+        <v>https://www.findmeglutenfree.com/biz/sunrose-7/5993868621643776</v>
       </c>
       <c r="Q1186" t="str">
         <v/>
@@ -77896,8 +77896,8 @@
       <c r="D1193" t="str">
         <v>landmark</v>
       </c>
-      <c r="E1193" t="str">
-        <v/>
+      <c r="E1193">
+        <v>0</v>
       </c>
       <c r="F1193" t="str">
         <v>🏰</v>
@@ -78026,8 +78026,8 @@
       <c r="D1195" t="str">
         <v>viewpoint</v>
       </c>
-      <c r="E1195" t="str">
-        <v/>
+      <c r="E1195">
+        <v>1</v>
       </c>
       <c r="F1195" t="str">
         <v>🌅</v>
@@ -78221,8 +78221,8 @@
       <c r="D1198" t="str">
         <v>landmark</v>
       </c>
-      <c r="E1198" t="str">
-        <v/>
+      <c r="E1198">
+        <v>1</v>
       </c>
       <c r="F1198" t="str">
         <v>🏰</v>
@@ -80093,9 +80093,74 @@
         <v/>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" t="str">
+        <v>Slovenia</v>
+      </c>
+      <c r="B1227" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="C1227" t="str">
+        <v>Sunrose 7 Restaurant</v>
+      </c>
+      <c r="D1227" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1227">
+        <v>1</v>
+      </c>
+      <c r="F1227" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1227" t="str">
+        <v>Sep/Oct</v>
+      </c>
+      <c r="H1227" t="str">
+        <v>2026</v>
+      </c>
+      <c r="I1227" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1227" t="str">
+        <v>46.271411</v>
+      </c>
+      <c r="K1227" t="str">
+        <v>13.95721</v>
+      </c>
+      <c r="L1227" t="str">
+        <v>Kelly (added 2026-10-10; restaurant inside Sunrose 7 hotel)</v>
+      </c>
+      <c r="M1227" t="str">
+        <v>Bohinj</v>
+      </c>
+      <c r="N1227" t="str">
+        <v/>
+      </c>
+      <c r="O1227" t="str">
+        <v>4-course tasting menu made GF pescatarian; unbelievable; added 4-glass wine pairing, so worth it; wish I had a second night.</v>
+      </c>
+      <c r="P1227" t="str">
+        <v>https://www.findmeglutenfree.com/biz/sunrose-7/5993868621643776</v>
+      </c>
+      <c r="Q1227">
+        <v>5</v>
+      </c>
+      <c r="R1227" t="str">
+        <v/>
+      </c>
+      <c r="S1227" t="str">
+        <v/>
+      </c>
+      <c r="T1227" t="str">
+        <v/>
+      </c>
+      <c r="U1227" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1226"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1227"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -79456,8 +79456,8 @@
       <c r="D1217" t="str">
         <v>other</v>
       </c>
-      <c r="E1217" t="str">
-        <v/>
+      <c r="E1217">
+        <v>1</v>
       </c>
       <c r="F1217" t="str">
         <v>📍</v>
